--- a/data/02_Daily_Sheets/Expressions_2026-05-27.xlsx
+++ b/data/02_Daily_Sheets/Expressions_2026-05-27.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ENG-20260527-163</t>
+          <t>ENG-20260527-262</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>hit a valuation / mark</t>
+          <t>hit a milestone</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -491,29 +491,29 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>/hɪt ə væljuˈeɪʃən / mɑːrk/</t>
+          <t>/hɪt ə ˈmaɪlˌstoʊn/</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>특정 가치나 목표치에 도달하다, 돌파하다.</t>
+          <t>중요한 이정표나 목표를 달성하다</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SK Hynix hits $1 trillion valuation as AI boom lifts South Korean chip stocks</t>
+          <t>SK Hynix hits $1 trillion valuation as AI boom lifts South Korean chip stocks. This company certainly hit a milestone.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The startup aims to hit a valuation of $10 billion within five years.</t>
+          <t>Our startup just hit a major milestone by securing Series B funding.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ENG-20260527-164</t>
+          <t>ENG-20260527-263</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>lift stock prices</t>
+          <t>send stocks soaring</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -538,29 +538,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>/lɪft stɑːk praɪsɪz/</t>
+          <t>/sɛnd stɑks ˈsɔrɪŋ/</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>주가를 끌어올리다, 상승시키다.</t>
+          <t>주가를 급등시키다</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AI boom lifts South Korean chip stocks</t>
+          <t>The AI boom lifts South Korean chip stocks, sending them soaring to new heights.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Positive earnings reports often lift stock prices across the market.</t>
+          <t>Positive earnings reports sent the company's stocks soaring this morning.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ENG-20260527-165</t>
+          <t>ENG-20260527-264</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>soar over X percent</t>
+          <t>top a record</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -585,29 +585,29 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>/sɔːr ˈoʊvər ɛks pərˌsɛnt/</t>
+          <t>/tɑp ə ˈrɛkərd/</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>(주가, 수치 등이) X퍼센트 이상 급등하다.</t>
+          <t>기록을 경신하다, 최고치를 넘다</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Shares of SK Hynix soared over 11% on Wednesday</t>
+          <t>South Korea's SK Hynix and U.S. chip firm Micron become the latest companies to top $1 trillion in market capitalization as the AI rally resumes.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>The company's revenue is expected to soar over 20% this quarter.</t>
+          <t>The latest sales figures show that we've topped a record in quarterly revenue.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ENG-20260527-166</t>
+          <t>ENG-20260527-265</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -622,39 +622,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>push something above a mark</t>
+          <t>do what it takes</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>/pʊʃ ˈsʌmθɪŋ əˈbʌv ə mɑːrk/</t>
+          <t>/du wʌt ɪt teɪks/</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>~을 특정 수준/기준점 이상으로 끌어올리다.</t>
+          <t>필요한 모든 조치를 취하다, 수단과 방법을 가리지 않다</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>pushing the South Korean memory-chip maker above the $1 trillion market capitalization mark.</t>
+          <t>ECB 'will do what is necessary' to tame inflation, meaning they will do what it takes.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Their innovative product could push the company's profits above its competitors.</t>
+          <t>We'll do what it takes to meet the project deadline, even if it means working overtime.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ENG-20260527-167</t>
+          <t>ENG-20260527-266</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>endorse someone</t>
+          <t>dash hopes</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -679,29 +679,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>/ɛnˈdɔːrs ˈsʌmwʌn/</t>
+          <t>/dæʃ hoʊps/</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>~를 공개적으로 지지하다.</t>
+          <t>기대를 좌절시키다, 희망을 꺾다</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>President Donald Trump last week endorsed Texas Attorney General Ken Paxton</t>
+          <t>Changing immigration rules and a weak hiring market dash hopes for international students seeking U.S. jobs.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Many celebrities endorsed the candidate, hoping to influence public opinion.</t>
+          <t>The unexpected downturn in the market dashed the hopes of many aspiring entrepreneurs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ENG-20260527-168</t>
+          <t>ENG-20260527-267</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -711,44 +711,44 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>reignite chatter / speculation</t>
+          <t>be behind something</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>/riːɪɡˈnaɪt ˈʧætər / ˌspɛkjuˈleɪʃən/</t>
+          <t>/bi bɪˈhaɪnd ˈsʌmθɪŋ/</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>(소문, 추측 등이) 다시 불붙다, 재점화되다.</t>
+          <t>어떤 일의 원인이 되다, 배후에 있다</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SpaceX-Tesla merger chatter reignites</t>
+          <t>'Bullying' and 'overbearing' behaviour behind abrupt BP chairman removal. That's what was behind his dismissal.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>The CEO's cryptic remarks reignited speculation about a potential acquisition.</t>
+          <t>We need to find out who is really behind these rumors.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ENG-20260527-169</t>
+          <t>ENG-20260527-268</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -758,44 +758,44 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>head for public markets</t>
+          <t>get away</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>/hɛd fɔːr ˈpʌblɪk ˈmɑːrkɪts/</t>
+          <t>/ɡɛt əˈweɪ/</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>(회사가) 주식 시장에 상장되다, 공모하다.</t>
+          <t>도망치다, 빠져나가다</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>With SpaceX headed for the public markets next month</t>
+          <t>The most unbelievable thing has happened. Underdog has just gotten away.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>The tech firm announced its plans to head for public markets early next year.</t>
+          <t>The suspect managed to get away from the police after a brief chase.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ENG-20260527-170</t>
+          <t>ENG-20260527-269</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -805,44 +805,44 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>speculate about something</t>
+          <t>be all over the news</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>/ˈspɛkjuˌleɪt əˈbaʊt ˈsʌmθɪŋ/</t>
+          <t>/bi ɔl ˈoʊvər ðə nuːz/</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>~에 대해 추측/짐작하다.</t>
+          <t>뉴스를 도배하다, 온통 뉴스에 나오다</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>industry experts and people close to Elon Musk are speculating about a potential tie-up with Tesla.</t>
+          <t>Of course the balloon. It's all over the news.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Analysts are speculating about the central bank's next move regarding interest rates.</t>
+          <t>The celebrity scandal was all over the news for weeks.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ENG-20260527-171</t>
+          <t>ENG-20260527-270</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -852,44 +852,44 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>form a tie-up</t>
+          <t>break free</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>/fɔːrm ə taɪ-ʌp/</t>
+          <t>/breɪk friː/</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>(회사 간의) 제휴/협력을 맺다.</t>
+          <t>탈출하다, 벗어나다</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>speculating about a potential tie-up with Tesla.</t>
+          <t>Right before he reached Macy's, he broke free and was spotted flying over Washington Square Park.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>The two companies decided to form a tie-up to develop new AI technologies.</t>
+          <t>The wild animal managed to break free from its enclosure.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ENG-20260527-172</t>
+          <t>ENG-20260527-271</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -899,44 +899,44 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>top an amount</t>
+          <t>let loose</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>/tɑːp ən əˈmaʊnt/</t>
+          <t>/lɛt luːs/</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>(금액/수치 면에서) ~를 넘어서다, 최고치를 기록하다.</t>
+          <t>(묶인 것을) 풀다; (감정이나 행동을) 마음껏 발산하다</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>the latest companies to top $1 trillion in market capitalization</t>
+          <t>Come on. An 80-foot inflatable dog let loose over the city. How often does that happen?</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>The blockbuster movie topped $1 billion in global box office revenue.</t>
+          <t>After a stressful week, I just want to let loose and dance.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ENG-20260527-173</t>
+          <t>ENG-20260527-272</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -946,44 +946,44 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>resume a rally</t>
+          <t>crouch down</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>/rɪˈzuːm ə ˈræli/</t>
+          <t>/kraʊtʃ daʊn/</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>(주가, 시장 등의) 반등세가 재개되다.</t>
+          <t>웅크리다, 쭈그리고 앉다</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>as the AI rally resumes.</t>
+          <t>Ok, ok, here we go. (he crouches down near her stomach) Ok, where am I talking to, here?</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>After a brief dip, the market is expected to resume a rally next week.</t>
+          <t>The photographer had to crouch down to get a good shot of the flowers.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ENG-20260527-174</t>
+          <t>ENG-20260527-273</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -993,44 +993,44 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>keep something secret</t>
+          <t>aim for</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>/kiːp ˈsʌmθɪŋ ˈsiːkrɪt/</t>
+          <t>/eɪm fɔr/</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>~를 비밀로 유지하다.</t>
+          <t>~을 목표로 하다, 겨냥하다</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>their name is being kept secret by a disciplinary panel.</t>
+          <t>Just aim for the bump.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>It's important to keep customer data secret to maintain trust.</t>
+          <t>Always aim for progress, not perfection.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ENG-20260527-175</t>
+          <t>ENG-20260527-274</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1040,44 +1040,44 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>hold below an amount</t>
+          <t>here goes</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>/hoʊld bɪˈloʊ ən əˈmaʊnt/</t>
+          <t>/hɪər ɡoʊz/</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>(가격 등이) 특정 금액/수준 아래를 유지하다.</t>
+          <t>자, 시작한다 (새로운/어려운 일을 시작할 때 쓰는 말)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>oil prices hold below $100</t>
+          <t>Ok, ok, ok, ok, here goes. You know, I, you know, can't do this.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>We hope the cost of raw materials will hold below our projected budget.</t>
+          <t>I'm about to give my presentation. Here goes nothing!</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ENG-20260527-176</t>
+          <t>ENG-20260527-275</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1087,44 +1087,44 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>assess operations / a situation</t>
+          <t>all over the place</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>/əˈsɛs ˌɑpəˈreɪʃənz / ə ˌsɪʧuˈeɪʃən/</t>
+          <t>/ɔl ˈoʊvər ðə pleɪs/</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>작전/상황을 평가하다, 검토하다.</t>
+          <t>여기저기 흩어져 있는; 두서없는, 엉망진창인</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>regional investors assess the latest military operations against Iran.</t>
+          <t>I loved the moment when you first saw the giant dog shadow all over the park.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>The committee will assess the situation and propose a course of action.</t>
+          <t>My thoughts were all over the place after hearing the shocking news.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ENG-20260527-177</t>
+          <t>ENG-20260527-276</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>double down on something</t>
+          <t>shoot down</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1149,29 +1149,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>/ˈdʌbl daʊn ɑn ˈsʌmθɪŋ/</t>
+          <t>/ʃuːt daʊn/</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>~에 더욱 전념하다, 투자를 강화하다.</t>
+          <t>(생각, 제안 등을) 거절하다, 묵살하다</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>European companies double down on China manufacturing</t>
+          <t>Yeah, but did they have to shoot him down? I mean, that was just mean.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Despite recent setbacks, the company decided to double down on its renewable energy investments.</t>
+          <t>My boss tends to shoot down any new ideas without even considering them.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ENG-20260527-178</t>
+          <t>ENG-20260527-277</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>de-risk supply chains</t>
+          <t>right about now</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1196,29 +1196,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>/diː-rɪsk səˈplaɪ ʧeɪnz/</t>
+          <t>/raɪt əˈbaʊt naʊ/</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>공급망의 위험을 줄이다.</t>
+          <t>바로 지금쯤</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>despite EU de-risking push</t>
+          <t>Ok, right about now the turkey should be crispy on the outside, juicy on the inside.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Governments are urging companies to de-risk supply chains by diversifying their suppliers.</t>
+          <t>The delivery should arrive right about now, so let's get ready.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ENG-20260527-179</t>
+          <t>ENG-20260527-278</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>reduce reliance on something</t>
+          <t>pick a major</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1243,29 +1243,29 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>/rɪˈduːs rɪˈlaɪəns ɑn ˈsʌmθɪŋ/</t>
+          <t>/pɪk ə ˈmeɪʤər/</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>~에 대한 의존도를 줄이다.</t>
+          <t>전공을 선택하다</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>reduce overseas reliance.</t>
+          <t>And everyone's telling me, you gotta pick a major, you gotta pick a major.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Many countries are trying to reduce reliance on imported oil.</t>
+          <t>It's difficult for many high school students to pick a major before they even start college.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ENG-20260527-180</t>
+          <t>ENG-20260527-279</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1275,44 +1275,44 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>grow barriers</t>
+          <t>on a dare</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>/ɡroʊ ˈbæriərz/</t>
+          <t>/ɑn ə dɛr/</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>(장벽이) 높아지다.</t>
+          <t>내기/도전으로, 장난 삼아</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Barriers grow for international students seeking U.S. jobs</t>
+          <t>So, on a dare, I picked paleontology.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Cultural differences can grow barriers to effective communication.</t>
+          <t>He ate the entire super spicy chili, just on a dare from his friends.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ENG-20260527-181</t>
+          <t>ENG-20260527-280</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1322,44 +1322,44 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>collapse a dream</t>
+          <t>have no idea</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>/kəˈlæps ə driːm/</t>
+          <t>/hæv noʊ aɪˈdiːə/</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>(꿈, 희망 등이) 좌절되다, 무너지다.</t>
+          <t>전혀 모르다</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>The 'American dream ... is collapsing'</t>
+          <t>And you have no idea what I'm saying, because, let's face it, you're a fetus.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>A sudden illness can unfortunately collapse one's dream of pursuing a career.</t>
+          <t>I have no idea how to fix this computer problem.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ENG-20260527-182</t>
+          <t>ENG-20260527-281</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1369,44 +1369,44 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>face a weak hiring market</t>
+          <t>let's face it</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>/feɪs ə wiːk ˈhaɪrɪŋ ˈmɑːrkɪt/</t>
+          <t>/lɛts feɪs ɪt/</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>고용 시장의 침체를 겪다.</t>
+          <t>솔직히 말해서, 현실을 직시하자면</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>International graduates say a weak hiring market... make it harder</t>
+          <t>And you have no idea what I'm saying, because, let's face it, you're a fetus.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>New graduates often face a weak hiring market during economic downturns.</t>
+          <t>Let's face it, we're not going to finish this project by tonight.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ENG-20260527-183</t>
+          <t>ENG-20260527-282</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1416,44 +1416,44 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>be entrenched in something</t>
+          <t>sing to</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>/biː ɛnˈtrɛnʧt ɪn ˈsʌmθɪŋ/</t>
+          <t>/sɪŋ tuː/</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>~에 깊이 빠져있다, ~에 뿌리박혀 있다.</t>
+          <t>~에게 노래를 불러주다</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Americans are 'entrenched' in financial stress amid debt and price pressures</t>
+          <t>Look, you don't have to talk to it. You can sing to it if you want.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>The company seems to be entrenched in outdated practices, resisting any change.</t>
+          <t>My grandmother used to sing to me every night before bed.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ENG-20260527-184</t>
+          <t>ENG-20260527-283</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>grapple with pressures</t>
+          <t>get looks from</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1478,29 +1478,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>/ˈɡræpl wɪθ ˈprɛʃərz/</t>
+          <t>/ɡɛt lʊks frʌm/</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>압력/어려움과 씨름하다, 고심하다.</t>
+          <t>~에게 시선을 받다, 주목받다</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>amid debt and price pressures</t>
+          <t>Here we come, walkin' down the street, get the funniest looks from, everyone we meet.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Businesses often grapple with pressures from rising costs and fierce competition.</t>
+          <t>She gets a lot of admiring looks from strangers when she wears that dress.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ENG-20260527-185</t>
+          <t>ENG-20260527-284</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1510,44 +1510,44 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>help with debt management</t>
+          <t>keep doing something</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>/hɛlp wɪð dɛt ˈmænɪʤmənt/</t>
+          <t>/kiːp ˈduːɪŋ ˈsʌmθɪŋ/</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>채무 관리를 돕다.</t>
+          <t>계속 ~하다</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Nonprofits can help with debt mangement.</t>
+          <t>Keep singing! Keep singing!</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Financial advisors can help with debt management and create a budget plan.</t>
+          <t>If you keep practicing, you'll definitely improve your skills.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ENG-20260527-186</t>
+          <t>ENG-20260527-285</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1557,44 +1557,44 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>energy bills rise</t>
+          <t>come out</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>/ˈɛnərʤi bɪlz raɪz/</t>
+          <t>/kʌm aʊt/</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>에너지 요금이 오르다.</t>
+          <t>나오다, 드러나다; (영화, 책 등이) 출시되다</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Energy bills to rise for millions as impact of Iran war hits</t>
+          <t>When you come out I'll buy you a bagel, and then we'll go to the zoo.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>With colder weather approaching, many expect their energy bills to rise.</t>
+          <t>The results of the election will come out sometime next week.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ENG-20260527-187</t>
+          <t>ENG-20260527-286</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1604,44 +1604,44 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>the impact of something hit</t>
+          <t>do the math</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>/ði ˈɪmpækt ʌv ˈsʌmθɪŋ hɪt/</t>
+          <t>/duː ðə mæθ/</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>~의 영향이 미치다.</t>
+          <t>계산해봐, 따져봐</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>as impact of Iran war hits</t>
+          <t>Hey, I got one keyhole and about a zillion keys. You do the math.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>The full impact of the new regulations will hit the industry next quarter.</t>
+          <t>If we only have 30 minutes for five presentations, do the math; each person gets six minutes.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ENG-20260527-188</t>
+          <t>ENG-20260527-287</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>pay X amount more</t>
+          <t>for an emergency</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1666,29 +1666,29 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>/peɪ ɛks əˈmaʊnt mɔːr/</t>
+          <t>/fɔr æn ɪˈmɜrʤənsi/</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>X 금액만큼 더 지불하다.</t>
+          <t>비상시를 대비하여</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>A household using a typical amount of energy will pay £221 a year more</t>
+          <t>(sarcastic) For an emergency just like this.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Consumers will have to pay 5% more for imported goods due to new tariffs.</t>
+          <t>Always keep a fully charged power bank for an emergency.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ENG-20260527-189</t>
+          <t>ENG-20260527-288</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1698,44 +1698,44 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>impose a price cap</t>
+          <t>if it wasn't for</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>/ɪmˈpoʊz ə praɪs kæp/</t>
+          <t>/ɪf ɪt wɑzənt fɔr/</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>가격 상한선을 부과하다/설정하다.</t>
+          <t>~가 아니었더라면</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>under the regulator's new price cap.</t>
+          <t>If it wasn't for you and your stupid balloon, I would be on a plane watching a woman do this right now.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>The government decided to impose a price cap on essential food items to help low-income families.</t>
+          <t>If it wasn't for my alarm clock, I would have overslept and missed my flight.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ENG-20260527-190</t>
+          <t>ENG-20260527-289</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1745,44 +1745,44 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>exhibit bullying behavior</t>
+          <t>swear by</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>/ɪɡˈzɪbɪt ˈbʊliɪŋ bɪˈheɪvjər/</t>
+          <t>/swɛər baɪ/</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>괴롭힘/갑질 행위를 보이다.</t>
+          <t>~을 맹신하다, ~의 효능/효과를 믿다</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>'Bullying' and 'overbearing' behaviour behind abrupt BP chairman removal</t>
+          <t>Monica: I swear you said you had the keys. Rachel: No, I didn't. (inspired by 'swear you said')</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>The company has a zero-tolerance policy for employees who exhibit bullying behavior.</t>
+          <t>My mom swears by this natural remedy for colds; she says it always works.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ENG-20260527-191</t>
+          <t>ENG-20260527-290</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>abruptly remove someone</t>
+          <t>aside from the fact that</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1807,29 +1807,29 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>/əˈbrʌptli rɪˈmuːv ˈsʌmwʌn/</t>
+          <t>/əˈsaɪd frʌm ðə fæk ðæt/</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>~를 갑작스럽게 해고하다/제거하다.</t>
+          <t>~라는 사실을 제외하면</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>abrupt BP chairman removal</t>
+          <t>Aside from the fact that you said you had them?</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>The board decided to abruptly remove the CEO following the scandal.</t>
+          <t>Aside from the fact that it's raining, it's a perfect day for a picnic.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ENG-20260527-192</t>
+          <t>ENG-20260527-291</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1839,44 +1839,44 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>join the list of something</t>
+          <t>hang out</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>/ʤɔɪn ðə lɪst ʌv ˈsʌmθɪŋ/</t>
+          <t>/hæŋ aʊt/</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>~의 명단에 합류하다.</t>
+          <t>어울려 놀다, 시간을 보내다</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SK Hynix and Micron are the latest tech firms to join the growing list of stocks with mega valuations.</t>
+          <t>Ross: Does it always, uh--? (A group of friends often hang out together)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>She hopes her novel will join the list of bestsellers this year.</t>
+          <t>Do you want to hang out at the coffee shop later?</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ENG-20260527-193</t>
+          <t>ENG-20260527-292</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1886,44 +1886,44 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>unveil a product</t>
+          <t>catch up</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>/ʌnˈveɪl ə ˈprɑːdʌkt/</t>
+          <t>/kætʃ ʌp/</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>신제품을 공개하다, 베일을 벗기다.</t>
+          <t>밀린 이야기를 나누다; (지연된 일을) 따라잡다</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>after it unveils first fully electric car</t>
+          <t>Monica: Ok, right about now the turkey should be crispy on the outside. (Friends often catch up on each other's lives)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>The tech giant is set to unveil its new smartphone at a highly anticipated event next month.</t>
+          <t>Let's grab lunch next week and catch up.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ENG-20260527-194</t>
+          <t>ENG-20260527-293</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1933,44 +1933,44 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>face intense pressure from someone</t>
+          <t>run into</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>/feɪs ɪnˈtɛns ˈprɛʃər frʌm ˈsʌmwʌn/</t>
+          <t>/rʌn ˈɪntuː/</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>~로부터 강한 압력을 받다.</t>
+          <t>우연히 마주치다</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>despite intense pressure from Chinese EV makers.</t>
+          <t>Rachel: I loved the moment when you first saw the giant dog shadow. (It's common to run into people in the city)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>The government is facing intense pressure from environmental groups to implement stricter regulations.</t>
+          <t>I ran into my old high school teacher at the grocery store yesterday.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ENG-20260527-195</t>
+          <t>ENG-20260527-294</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1980,44 +1980,44 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>issue a warning</t>
+          <t>mess up</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>/ˈɪʃuː ə ˈwɔːrnɪŋ/</t>
+          <t>/mɛs ʌp/</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경고를 발하다/내놓다.</t>
+          <t>망치다, 실수하다</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Farmers' warning as milk prices fall below cost</t>
+          <t>Phoebe: Oh, I'm sorry, oh, I just, I thought we could have them whipped. (Phoebe felt like she messed up the potatoes)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>The meteorology office issued a warning for heavy rain and strong winds.</t>
+          <t>I really messed up my presentation; I forgot half of what I wanted to say.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ENG-20260527-196</t>
+          <t>ENG-20260527-295</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2027,44 +2027,44 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>sell family farms</t>
+          <t>call off</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>/sɛl ˈfæməli fɑːrmz/</t>
+          <t>/kɔl ɔf/</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>가업 농장을 팔다.</t>
+          <t>취소하다</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Farmers worry more family farms will be sold unless dairy prices rise quickly.</t>
+          <t>Chandler: The most unbelievable thing has happened. (Sometimes plans get called off unexpectedly)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Many small farmers are struggling and may have to sell family farms to survive.</t>
+          <t>They had to call off the outdoor concert due to heavy rain.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ENG-20260527-197</t>
+          <t>ENG-20260527-296</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2074,44 +2074,44 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ads be banned</t>
+          <t>turn down</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>/ædz biː bænd/</t>
+          <t>/tɜrn daʊn/</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>광고가 금지되다.</t>
+          <t>거절하다; (소리, 불빛 등을) 줄이다</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Instagram betting ads featuring Kane and Haaland banned</t>
+          <t>Carol: So don't do it, it's fine. You don't have to do it just because Susan does it. (Ross wanted to turn down the offer to sing)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Many controversial ads were banned from television during prime time.</t>
+          <t>I had to turn down the job offer because it wasn't a good fit for me.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ENG-20260527-198</t>
+          <t>ENG-20260527-297</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2121,44 +2121,44 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>make it harder for someone to do something</t>
+          <t>go through</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>/meɪk ɪt ˈhɑːrdər fɔːr ˈsʌmwʌn tuː duː ˈsʌmθɪŋ/</t>
+          <t>/ɡoʊ θruː/</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>~가 ~하기 더 어렵게 만들다.</t>
+          <t>겪다, 경험하다; (서류 등을) 검토하다</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>AI tools like Mythos will make it harder for people like her to compete.</t>
+          <t>Ross: And everyone's telling me, you gotta pick a major. (He's going through a lot of pressure)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Lack of funding will make it harder for researchers to complete their projects on time.</t>
+          <t>She's going through a difficult time after losing her job.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ENG-20260527-199</t>
+          <t>ENG-20260527-298</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2168,44 +2168,44 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>compete fiercely</t>
+          <t>pull off</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>/kəmˈpiːt ˈfɪrsli/</t>
+          <t>/pʊl ɔf/</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>치열하게 경쟁하다.</t>
+          <t>성공적으로 해내다, 해치우다</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>make competing harder</t>
+          <t>Joey: Hey, I got one keyhole and about a zillion keys. You do the math. (Pulling off opening the door with so many keys would be impressive)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>In today's global market, companies must innovate to compete fiercely.</t>
+          <t>I can't believe they managed to pull off such a complex event with so little planning.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ENG-20260527-200</t>
+          <t>ENG-20260527-299</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2215,44 +2215,44 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>delay an investigation</t>
+          <t>get over</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>/dɪˈleɪ ən ɪnˌvɛstɪˈɡeɪʃən/</t>
+          <t>/ɡɛt ˈoʊvər/</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>조사를 지연시키다.</t>
+          <t>(문제, 어려움, 병 등을) 극복하다; (상대방에 대한 감정을) 잊다</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Post Office investigation could be delayed by five years</t>
+          <t>Phoebe: Yeah, but did they have to shoot him down? I mean, that was just mean. (It's hard to get over mean actions)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Unexpected obstacles could delay an investigation into the cause of the accident.</t>
+          <t>It took her a long time to get over the breakup.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ENG-20260527-201</t>
+          <t>ENG-20260527-300</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2262,44 +2262,44 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>welcome a move / plan</t>
+          <t>look up to</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>/ˈwɛlkəm ə muːv / plæn/</t>
+          <t>/lʊk ʌp tuː/</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>(정부 등의) 조치/계획을 환영하다.</t>
+          <t>~을 존경하다, 우러러보다</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Campaigners welcome the move but say passengers are mostly worried about train fares and delays.</t>
+          <t>Susan: I felt it! Ross: (singin) Hey, hey, I'm your daddy. (A child might look up to their father)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Environmentalists welcome a new government plan to reduce carbon emissions.</t>
+          <t>Many young athletes look up to professional sports stars as role models.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ENG-20260527-202</t>
+          <t>ENG-20260527-301</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2309,44 +2309,44 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>be worried about something</t>
+          <t>put off</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>/biː ˈwɜːrid əˈbaʊt ˈsʌmθɪŋ/</t>
+          <t>/pʊt ɔf/</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>~에 대해 걱정하다, 염려하다.</t>
+          <t>연기하다, 미루다; ~에게 불쾌감을 주다</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>passengers are mostly worried about train fares and delays.</t>
+          <t>Monica: Can you go any faster with that? (Joey was putting off finding the right key)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Parents are worried about their children's safety at school.</t>
+          <t>Don't put off your homework until the last minute.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ENG-20260527-203</t>
+          <t>ENG-20260527-302</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2356,44 +2356,44 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>experience a dramatic fall</t>
+          <t>deal with</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>/ɪkˈspɪəriəns ə drəˈmætɪk fɔːl/</t>
+          <t>/dil wɪð/</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>급격한 하락/감소를 겪다.</t>
+          <t>다루다, 처리하다</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Lord Wolfson warns of 'dramatic' fall in entry-level jobs</t>
+          <t>Monica: (panicked) The oven is on. (They needed to deal with the locked door situation)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>The tourism industry experienced a dramatic fall in visitors during the pandemic.</t>
+          <t>The customer service team is trained to deal with difficult complaints calmly.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ENG-20260527-204</t>
+          <t>ENG-20260527-303</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2403,44 +2403,44 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>receive a number of applicants</t>
+          <t>figure out</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>/rɪˈsiːv ə ˈnʌmbər ʌv ˈæplɪkənts/</t>
+          <t>/ˈfɪɡjər aʊt/</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>~명의 지원자를 받다.</t>
+          <t>알아내다, 이해하다; 해결하다</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Next now typically receives double the number of applicants for one role than it did two years ago.</t>
+          <t>Rachel: I swear you said you had the keys. Monica: But I didn't. (They needed to figure out who had the keys)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Our internship program received a record number of applicants this year.</t>
+          <t>I'm trying to figure out how to install this new software.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ENG-20260527-205</t>
+          <t>ENG-20260527-304</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2455,39 +2455,39 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>get someone another drink</t>
+          <t>come across</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>/ɡɛt ˈsʌmwʌn əˈnʌðər drɪŋk/</t>
+          <t>/kʌm əˈkrɔs/</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>~에게 술/음료 한 잔 더 가져다주다.</t>
+          <t>우연히 발견하다; ~라는 인상을 주다</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Can I get you another glass of wine?</t>
+          <t>Phoebe: Oh, I'm sorry, oh, I just, I thought we could have them whipped. (Monica came across as demanding)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>The waiter asked if he could get us another drink.</t>
+          <t>I came across an old photo album while cleaning the attic.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ENG-20260527-206</t>
+          <t>ENG-20260527-305</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2502,39 +2502,39 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>be drunk</t>
+          <t>fall apart</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>/biː drʌŋk/</t>
+          <t>/fɔl əˈpɑrt/</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>술에 취하다.</t>
+          <t>허물어지다, 무너지다; 붕괴하다</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>I don't wanna be drunk when I go home alone.</t>
+          <t>Ross: I can't do this. Uh, this is too weird. I feel stupid. (Ross felt like he was falling apart under pressure)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>It's dangerous to drive when you're drunk.</t>
+          <t>After the scandal, the company's reputation started to fall apart.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ENG-20260527-207</t>
+          <t>ENG-20260527-306</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>stand someone up</t>
+          <t>patch things up</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2559,29 +2559,29 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>/stænd ˈsʌmwʌn ʌp/</t>
+          <t>/pætʃ θɪŋz ʌp/</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>~를 바람맞히다, 약속 장소에 나타나지 않다.</t>
+          <t>관계를 회복하다, 화해하다</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Got stood up, huh?</t>
+          <t>Rachel: I swear you said you had the keys. Monica: But I didn't. (Monica and Rachel need to patch things up after their argument)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>I can't believe he stood me up on our first date!</t>
+          <t>After their big fight, John and Sarah decided to patch things up.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ENG-20260527-208</t>
+          <t>ENG-20260527-307</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2596,39 +2596,39 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>be no big deal</t>
+          <t>fill someone in</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>/biː noʊ bɪɡ diːl/</t>
+          <t>/fɪl ˈsʌmˌwʌn ɪn/</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>별일 아니다, 대수롭지 않다.</t>
+          <t>~에게 소식을 전하다, 상황을 알려주다</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Yeah, it's no big deal. It's just a blind date.</t>
+          <t>Chandler: The most unbelievable thing has happened. Underdog has just gotten away. (He's filling them in on the news)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Don't worry about the spilled coffee; it's no big deal.</t>
+          <t>I missed the meeting, so can you fill me in on what was discussed?</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ENG-20260527-209</t>
+          <t>ENG-20260527-308</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2643,39 +2643,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>go on a blind date</t>
+          <t>nod off</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>/ɡoʊ ɑn ə blaɪnd deɪt/</t>
+          <t>/nɑd ɔf/</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>소개팅을 하다.</t>
+          <t>꾸벅꾸벅 졸다</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>It's just a blind date.</t>
+          <t>Ross: And you have no idea what I'm saying, because, let's face it, you're a fetus. (A fetus would nod off during a long speech)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>My friend tried to set me up, but I'm hesitant to go on a blind date.</t>
+          <t>The lecture was so boring that I kept nodding off in my seat.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ENG-20260527-210</t>
+          <t>ENG-20260527-309</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>emerge from somewhere</t>
+          <t>brush off</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2700,29 +2700,29 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>/ɪˈmɜːrdʒ frʌm ˈsʌmˌwɛr/</t>
+          <t>/brʌʃ ɔf/</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>~에서 나오다, 나타나다.</t>
+          <t>묵살하다, 무시하다</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Monica emerges from the bathroom.</t>
+          <t>Phoebe: Yeah, but did they have to shoot him down? (The authorities might brush off public complaints)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>The celebrity emerged from the hotel to a crowd of cheering fans.</t>
+          <t>He tried to brush off my concerns, but I insisted on discussing them.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ENG-20260527-211</t>
+          <t>ENG-20260527-310</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2737,39 +2737,39 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>be ovulating</t>
+          <t>talk over</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>/biː ˈɑːvjəleɪtɪŋ/</t>
+          <t>/tɔk ˈoʊvər/</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>배란 중이다.</t>
+          <t>상의하다, ~에 대해 논의하다</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>We're okay. I'm still ovulating.</t>
+          <t>Rachel: I swear you said you had the keys. Monica: But I didn't. (They should talk over the key situation calmly)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Many women track their cycle to know when they are ovulating.</t>
+          <t>Let's talk over the project details before making any final decisions.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ENG-20260527-212</t>
+          <t>ENG-20260527-311</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2784,39 +2784,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>as of X time / date</t>
+          <t>butt in</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>/æz ʌv ɛks taɪm / deɪt/</t>
+          <t>/bʌt ɪn/</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>X 시점/날짜부로.</t>
+          <t>(대화나 일에) 끼어들다, 참견하다</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>as of four o'clock this afternoon, I am not.</t>
+          <t>Phoebe: Ooh, ok, that's it. Enough with the keys. No one say keys. (She butted in to stop the argument)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>The new policy will be effective as of January 1st.</t>
+          <t>It's rude to butt in when other people are talking.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ENG-20260527-213</t>
+          <t>ENG-20260527-312</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2831,39 +2831,39 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>give it a minute</t>
+          <t>bail on</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>/ɡɪv ɪt ə ˈmɪnɪt/</t>
+          <t>/beɪl ɑn/</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>잠깐만 기다려봐, 잠시 시간을 줘.</t>
+          <t>(약속, 책임 등을) 저버리다, 바람맞히다</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>I know you're not eighteen anymore, but give it a minute.</t>
+          <t>Rachel: I can't, I gotta go. (She had to bail on going to the roof)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>The system is rebooting; just give it a minute.</t>
+          <t>He bailed on our dinner plans at the last minute.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ENG-20260527-214</t>
+          <t>ENG-20260527-313</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2878,39 +2878,39 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>forget someone is here</t>
+          <t>chicken out</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>/fərˈɡɛt ˈsʌmwʌn ɪz hɪr/</t>
+          <t>/ˈʧɪkɪn aʊt/</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>~가 여기 있다는 것을 잊다.</t>
+          <t>겁먹고 포기하다, 꽁무니 빼다</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Oh, sweetie, I forgot you were here.</t>
+          <t>Ross: Ok, ok, ok, ok, here goes. You know, I, you know, can't do this. Uh, this is too weird. I feel stupid. (Ross almost chickened out of talking to Carol's belly)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>I'm sorry, I was so engrossed in my work, I completely forgot you were here.</t>
+          <t>I was going to try skydiving, but I chickened out at the last moment.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ENG-20260527-215</t>
+          <t>ENG-20260527-314</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>leave someone alone</t>
+          <t>fend off</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2935,29 +2935,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>/liːv ˈsʌmwʌn əˈloʊn/</t>
+          <t>/fɛnd ɔf/</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>~를 혼자 내버려두다.</t>
+          <t>~을 물리치다, 막아내다</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>We can't leave her alone.</t>
+          <t>European companies double down on China manufacturing despite EU de-risking push. (Companies need to fend off pressure from EU.)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Please leave me alone; I need some time to think.</t>
+          <t>The politician had to fend off tough questions from reporters during the press conference.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ENG-20260527-216</t>
+          <t>ENG-20260527-315</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2967,44 +2967,44 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>be aware of something</t>
+          <t>pencil in</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>/biː əˈwɛr ʌv ˈsʌmθɪŋ/</t>
+          <t>/ˈpɛnsəl ɪn/</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>~를 인지하다, 인식하다.</t>
+          <t>임시로 일정을 잡다</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>how much can she even be aware of at this age?</t>
+          <t>The Post Office investigation could be delayed by five years, police warn. (They need to pencil in new timelines)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Are you aware of the potential risks involved in this investment?</t>
+          <t>Let's pencil in a meeting for Tuesday afternoon, and I'll confirm with everyone.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ENG-20260527-217</t>
+          <t>ENG-20260527-316</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3014,44 +3014,44 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>start canoodling</t>
+          <t>rule out</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>/stɑːrt kəˈnuːdlɪŋ/</t>
+          <t>/rul aʊt/</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>(특히 공공장소에서) 애정 행각을 시작하다.</t>
+          <t>배제하다, ~의 가능성을 없애다</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>She may notice if we start... canoodling in it.</t>
+          <t>The commander leading the national police inquiry needs to rule out other possibilities.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>They started canoodling in the park, much to the amusement of passersby.</t>
+          <t>The detective couldn't rule out the possibility of foul play.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ENG-20260527-218</t>
+          <t>ENG-20260527-317</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3061,44 +3061,44 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>say something in front of someone</t>
+          <t>wear off</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>/seɪ ˈsʌmθɪŋ ɪn frʌnt ʌv ˈsʌmwʌn/</t>
+          <t>/wɛər ɔf/</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>~ 앞에서 ~를 말하다.</t>
+          <t>점점 사라지다, 효과가 없어지다</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>I can't say "hump" or "screw" in front of the B-A-B-Y.</t>
+          <t>Energy bills to rise for millions as impact of Iran war hits. (The relief of lower prices will wear off)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>You shouldn't say such things in front of children.</t>
+          <t>The initial excitement of the new job started to wear off after a few months.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ENG-20260527-219</t>
+          <t>ENG-20260527-318</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3108,44 +3108,44 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>be horrifying / scarring</t>
+          <t>go back on</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>/biː ˈhɔːrəˌfaɪɪŋ / ˈskɑːrɪŋ/</t>
+          <t>/ɡoʊ bæk ɑn/</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>소름끼치다 / 트라우마를 남기다.</t>
+          <t>(약속, 합의 등을) 어기다, 철회하다</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Horrifying? Scarring?</t>
+          <t>European companies double down on China manufacturing despite EU de-risking push. (EU feels they go back on agreements)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>The images of the war were truly horrifying and scarring.</t>
+          <t>He's known for always keeping his word and never going back on a promise.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ENG-20260527-220</t>
+          <t>ENG-20260527-319</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3155,44 +3155,44 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>guess someone is right</t>
+          <t>touch base</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>/ɡɛs ˈsʌmwʌn ɪz raɪt/</t>
+          <t>/tʌtʃ beɪs/</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>~의 말이 맞는 것 같다.</t>
+          <t>간략히 연락하다, 안부를 묻거나 상황을 확인하다</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>I guess you're right.</t>
+          <t>With SpaceX headed for the public markets next month, industry experts and people close to Elon Musk are speculating about a potential tie-up with Tesla. (They need to touch base with Musk's team)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>After reconsidering the facts, I guess you're right about the solution.</t>
+          <t>Let's touch base next week to discuss the progress of the project.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ENG-20260527-221</t>
+          <t>ENG-20260527-320</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3202,44 +3202,44 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>stare through something</t>
+          <t>circle back</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>/stɛr θruː ˈsʌmθɪŋ/</t>
+          <t>/ˈsɜrkəl bæk/</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>~를 통해 응시하다.</t>
+          <t>(나중에) 다시 논의하다, 재론하다</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>you thought a deer was staring through the window.</t>
+          <t>The ECB 'will do what is necessary' to tame inflation. (They might need to circle back to their strategies)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>She stared through the rain-streaked window, lost in thought.</t>
+          <t>That's a good point, but let's circle back to it after we've covered the main agenda items.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ENG-20260527-222</t>
+          <t>ENG-20260527-321</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3249,44 +3249,44 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>be out of someone's league</t>
+          <t>hit a snag</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>/biː aʊt ʌv ˈsʌmwʌnz liːɡ/</t>
+          <t>/hɪt ə snæɡ/</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>~의 수준을 훨씬 벗어나다, 넘사벽이다.</t>
+          <t>예상치 못한 문제에 부딪히다</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Oh, come on, you're way out of my league.</t>
+          <t>The Post Office investigation could be delayed by five years, police warn. (The investigation hit a snag)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>He's a famous supermodel; she felt he was completely out of her league.</t>
+          <t>Our plans to launch the new product hit a snag when we encountered a supply chain issue.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ENG-20260527-223</t>
+          <t>ENG-20260527-322</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3296,44 +3296,44 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>rule out something</t>
+          <t>drive a hard bargain</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>/ruːl aʊt ˈsʌmθɪŋ/</t>
+          <t>/draɪv ə hɑrd ˈbɑrɡɪn/</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>~를 배제하다, 가능성을 제외하다.</t>
+          <t>흥정을 잘하다, 타협하지 않고 유리한 조건을 얻으려 하다</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>let's not rule out nervous laughter.</t>
+          <t>European companies double down on China manufacturing despite EU de-risking push. (China often drives a hard bargain)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Investigators have not ruled out the possibility of foul play.</t>
+          <t>He's known for being a tough negotiator; he always drives a hard bargain.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ENG-20260527-224</t>
+          <t>ENG-20260527-323</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>own a business</t>
+          <t>take the hit</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3358,29 +3358,29 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>/oʊn ə ˈbɪznɪs/</t>
+          <t>/teɪk ðə hɪt/</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>사업체를 소유하다, 운영하다.</t>
+          <t>손해를 감수하다, 비난을 받다</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Phoebe told me that - that you owned your own restaurant.</t>
+          <t>Energy bills to rise for millions as impact of Iran war hits. (Households will take the hit)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>It's always been my dream to own a business and be my own boss.</t>
+          <t>The company decided to take the hit on profits rather than raise prices for loyal customers.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ENG-20260527-225</t>
+          <t>ENG-20260527-324</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3390,12 +3390,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>lose something to something else</t>
+          <t>call the shots</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3405,29 +3405,29 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>/luːz ˈsʌmθɪŋ tuː ˈsʌmθɪŋ ɛls/</t>
+          <t>/kɔl ðə ʃɑts/</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>~때문에 ~를 잃다.</t>
+          <t>결정권을 쥐다, 지휘하다</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>I lost it. To drugs.</t>
+          <t>President Donald Trump last week endorsed Texas Attorney General Ken Paxton. (He calls the shots in his party)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Many people lose their savings to risky investments.</t>
+          <t>As the project manager, she's the one who calls the shots.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ENG-20260527-226</t>
+          <t>ENG-20260527-325</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>do something for no money</t>
+          <t>clear the air</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3452,29 +3452,29 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>/duː ˈsʌmθɪŋ fɔːr noʊ ˈmʌni/</t>
+          <t>/klɪər ðɪ ɛər/</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>무급으로 ~를 하다, 돈을 받지 않고 ~를 하다.</t>
+          <t>오해를 풀다, 관계를 명확히 하다</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>It's really fulfilling doing something you hate for no money.</t>
+          <t>Rachel: I swear you said you had the keys. Monica: But I didn't. (They need to clear the air after their argument)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Volunteers often do something for no money simply because they believe in the cause.</t>
+          <t>After their disagreement, they decided to meet for coffee to clear the air.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ENG-20260527-227</t>
+          <t>ENG-20260527-326</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>be infertile</t>
+          <t>give someone a heads-up</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3499,29 +3499,29 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>/biː ɪnˈfɜːrtaɪl/</t>
+          <t>/ɡɪv ˈsʌmˌwʌn ə ˈhɛdz ʌp/</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>불임이다.</t>
+          <t>~에게 미리 알려주다, 경고하다</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>I'm pretty sure I'm infertile.</t>
+          <t>Chandler: The most unbelievable thing has happened. Underdog has just gotten away. (He gave them a heads-up about the balloon.)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>The couple was heartbroken to learn they were infertile.</t>
+          <t>Can you give me a heads-up if there are any changes to the schedule?</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ENG-20260527-228</t>
+          <t>ENG-20260527-327</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3536,39 +3536,39 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>hunt someone down</t>
+          <t>pull some strings</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>/hʌnt ˈsʌmwʌn daʊn/</t>
+          <t>/pʊl sʌm strɪŋz/</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>~를 추적하여 찾아내다.</t>
+          <t>배후에서 영향력을 행사하다, (인맥을 동원해) 일을 해결하다</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>I'm going to hunt you down and kill you!</t>
+          <t>Joey: We have a copy of your key. (Joey might have to pull some strings to get the key faster.)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>The detective vowed to hunt down the culprits and bring them to justice.</t>
+          <t>I had to pull some strings to get us tickets for the sold-out concert.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ENG-20260527-229</t>
+          <t>ENG-20260527-328</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3583,39 +3583,39 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>set someone up with someone</t>
+          <t>read the room</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>/sɛt ˈsʌmwʌn ʌp wɪð ˈsʌmwʌn/</t>
+          <t>/rid ðə rum/</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>~를 ~와 소개시켜 주다.</t>
+          <t>분위기를 파악하다, 상황을 읽다</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>How could you set me up with this creep?</t>
+          <t>Ross: I can't do this. Uh, this is too weird. I feel stupid. (He couldn't read the room well enough to just relax)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>My sister tried to set me up with her colleague, but I politely declined.</t>
+          <t>A good comedian knows how to read the room and adjust their jokes accordingly.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ENG-20260527-230</t>
+          <t>ENG-20260527-329</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>be a nightmare</t>
+          <t>take something with a grain of salt</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3640,29 +3640,29 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>/biː ə ˈnaɪtˌmɛr/</t>
+          <t>/teɪk ˈsʌmθɪŋ wɪθ ə ɡreɪn ʌv sɔlt/</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>(사람/상황이) 정말 지긋지긋하다/끔찍하다.</t>
+          <t>~을 액면 그대로 믿지 않다, 흘려듣다</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>This guy is a nightmare!</t>
+          <t>SpaceX-Tesla merger chatter reignites as Musk pushes rocket company towards Nasdaq. (One should take merger rumors with a grain of salt.)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Planning a wedding can sometimes be a nightmare, with all the details.</t>
+          <t>You should take his promises with a grain of salt; he often exaggerates.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ENG-20260527-231</t>
+          <t>ENG-20260527-330</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>get stoned</t>
+          <t>buy time</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3687,29 +3687,29 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>/ɡɛt stoʊnd/</t>
+          <t>/baɪ taɪm/</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>마리화나 등에 취하다.</t>
+          <t>시간을 벌다</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>he gets a little crazy when he's stoned.</t>
+          <t>The Post Office investigation could be delayed by five years. (This delay buys them time.)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Some people experiment with drugs to get stoned, but it's very dangerous.</t>
+          <t>We need to buy time to prepare a better proposal for the client.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ENG-20260527-232</t>
+          <t>ENG-20260527-331</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3719,44 +3719,44 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>go out for something</t>
+          <t>cut corners</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>/ɡoʊ aʊt fɔːr ˈsʌmθɪŋ/</t>
+          <t>/kʌt ˈkɔrnərz/</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>~를 하러 나가다.</t>
+          <t>절차를 무시하고 대충 하다, 비용이나 노력을 절감하다</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Did he go out for a cigarette?</t>
+          <t>European companies double down on China manufacturing despite EU de-risking push. (Some companies cut corners on safety)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Let's go out for a quick lunch during our break.</t>
+          <t>Don't cut corners on quality just to save a little money; it will cost more in the long run.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ENG-20260527-233</t>
+          <t>ENG-20260527-332</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3766,44 +3766,44 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>hang up in disgust</t>
+          <t>face the music</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>/hæŋ ʌp ɪn dɪsˈɡʌst/</t>
+          <t>/feɪs ðə ˈmjuːzɪk/</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>혐오감에 전화를 끊다.</t>
+          <t>잘못에 대한 비난/벌을 받다, 결과를 감수하다</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Rachel hangs up in disgust.)</t>
+          <t>BP chairman removed due to 'bullying' behavior. He had to face the music.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>After listening to his insults, she hung up in disgust.</t>
+          <t>After neglecting his responsibilities, he finally had to face the music and deal with the consequences.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ENG-20260527-234</t>
+          <t>ENG-20260527-333</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>have a miserable time</t>
+          <t>have second thoughts</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3828,29 +3828,29 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>/hæv ə ˈmɪzərəbl taɪm/</t>
+          <t>/hæv ˈsɛkənd θɔts/</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>비참한/끔찍한 시간을 보내다.</t>
+          <t>다시 생각하다, 재고하다</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Rachel is having a miserable time</t>
+          <t>Ross: Ok, ok, ok, ok, here goes. You know, I, you know, can't do this. (He was having second thoughts about talking to the belly.)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>If the weather is bad, we might have a miserable time at the outdoor concert.</t>
+          <t>I'm having second thoughts about accepting that job offer; it seems a bit risky.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ENG-20260527-235</t>
+          <t>ENG-20260527-334</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3860,44 +3860,44 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>figure out something</t>
+          <t>make ends meet</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>/ˈfɪɡjər aʊt ˈsʌmθɪŋ/</t>
+          <t>/meɪk ɛndz mit/</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>~를 알아내다, 이해하다, 해결하다.</t>
+          <t>수입과 지출의 균형을 맞추다, 겨우 생계를 유지하다</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>By the time anyone's figured out what we've done</t>
+          <t>Americans are 'entrenched' in financial stress amid debt and price pressures. (Many struggle to make ends meet.)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>I'm trying to figure out how to solve this complex math problem.</t>
+          <t>It's becoming increasingly difficult for families to make ends meet with the rising cost of living.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ENG-20260527-236</t>
+          <t>ENG-20260527-335</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3912,39 +3912,39 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>fall asleep</t>
+          <t>play it by ear</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>/fɔːl əˈsliːp/</t>
+          <t>/pleɪ ɪt baɪ iər/</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>잠들다.</t>
+          <t>상황 봐서 즉흥적으로 처리하다</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Emma has fallen asleep in her playpen, and Chandler has fallen asleep right next to her on the floor.</t>
+          <t>Rachel: We're waiting for you to open the door. You got the keys. (They might have to play it by ear to get inside.)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>I was so tired that I fell asleep as soon as my head hit the pillow.</t>
+          <t>We don't have a strict plan for the weekend; let's just play it by ear.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ENG-20260527-237</t>
+          <t>ENG-20260527-336</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3959,39 +3959,39 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>suck on something</t>
+          <t>sleep on it</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>/sʌk ɑn ˈsʌmθɪŋ/</t>
+          <t>/slip ɑn ɪt/</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>~를 빨다.</t>
+          <t>하룻밤 자면서 곰곰이 생각하다 (결정을 미루다)</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>He's even sucking on a pacifier.</t>
+          <t>Carol: So don't do it, it's fine. You don't have to do it just because Susan does it. (Ross could sleep on it before deciding to sing)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Babies often suck on their thumbs for comfort.</t>
+          <t>That's a big decision, so why don't you sleep on it and tell me your answer tomorrow?</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ENG-20260527-238</t>
+          <t>ENG-20260527-337</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4006,39 +4006,39 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>wake up</t>
+          <t>take a rain check</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>/weɪk ʌp/</t>
+          <t>/teɪk ə reɪn tʃɛk/</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>잠에서 깨다.</t>
+          <t>다음 기회로 미루다, (초대를) 나중에 받아들이다</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Chandler wakes up and looks a bit confused</t>
+          <t>Rachel: I can't, I gotta go. (She had to take a rain check on going to the roof.)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>I always wake up early on weekends to enjoy the quiet morning.</t>
+          <t>I'm too busy to go out tonight, but can I take a rain check?</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ENG-20260527-239</t>
+          <t>ENG-20260527-338</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4048,44 +4048,44 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>make noise</t>
+          <t>miss the boat</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>/meɪk nɔɪz/</t>
+          <t>/mɪs ðə boʊt/</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>소음을 내다.</t>
+          <t>기회를 놓치다</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>And you can't make any noise.</t>
+          <t>SK Hynix hits $1 trillion valuation as AI boom lifts South Korean chip stocks. (Investors who didn't buy early missed the boat.)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Please try not to make noise when you leave, as the baby is sleeping.</t>
+          <t>If you don't apply for the scholarship soon, you'll miss the boat.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ENG-20260527-240</t>
+          <t>ENG-20260527-339</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4095,44 +4095,44 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>navigate financial hardship</t>
+          <t>pick someone's brain</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>/ˈnævɪɡeɪt faɪˈnænʃəl ˈhɑːrdʃɪp/</t>
+          <t>/pɪk ˈsʌmˌwʌnz breɪn/</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>재정적 어려움을 헤쳐나가다.</t>
+          <t>~에게 조언을 구하다, 지식을 얻다</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Americans are 'entrenched' in financial stress amid debt and price pressures</t>
+          <t>Chompie, one of the world's tops ethical hackers, says AI like Claude Mythos will make it harder for people like her to compete. (Perhaps others want to pick Chompie's brain.)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Many families are struggling to navigate financial hardship in the current economy.</t>
+          <t>I'd love to pick your brain sometime about your experience in the tech industry.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ENG-20260527-241</t>
+          <t>ENG-20260527-340</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4142,44 +4142,44 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>reach mega valuations</t>
+          <t>tighten the belt</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>/riːʧ ˈmɛɡə væljuˈeɪʃənz/</t>
+          <t>/ˈtaɪtən ðə bɛlt/</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>엄청난 기업 가치에 도달하다.</t>
+          <t>허리띠를 졸라매다, 지출을 줄이다</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>the growing list of stocks with mega valuations.</t>
+          <t>Americans are 'entrenched' in financial stress amid debt and price pressures. (Many have to tighten their belts.)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Successful tech companies can reach mega valuations within just a few years.</t>
+          <t>With rising inflation, many families are having to tighten their belts and cut back on non-essential spending.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ENG-20260527-242</t>
+          <t>ENG-20260527-341</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4189,44 +4189,44 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>draw divided opinion</t>
+          <t>call it a day</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>/drɔː dɪˈvaɪdɪd əˈpɪnjən/</t>
+          <t>/kɔl ɪt ə deɪ/</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>의견을 양분시키다, 상반된 반응을 이끌어내다.</t>
+          <t>하루 일을 마치다, 끝내다</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>The new Luce model has divided opinion on social media</t>
+          <t>Ok, all done. (Phoebe was ready to call it a day on the potatoes)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>The art exhibition drew divided opinion from critics, with some praising it and others condemning it.</t>
+          <t>It's getting late; let's call it a day and pick this up tomorrow morning.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ENG-20260527-243</t>
+          <t>ENG-20260527-342</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4236,44 +4236,44 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>secure an entry-level job</t>
+          <t>spill the beans</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>/sɪˈkjʊr ən ˈɛntri-ˈlɛvl ʤɑːb/</t>
+          <t>/spɪl ðə binz/</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>신입 일자리를 얻다/확보하다.</t>
+          <t>비밀을 누설하다, 다 불어버리다</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>'dramatic' fall in entry-level jobs</t>
+          <t>Chandler: The most unbelievable thing has happened. Underdog has just gotten away. (He's spilling the beans about the event.)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>It can be challenging for recent graduates to secure an entry-level job without prior experience.</t>
+          <t>Don't spill the beans about the surprise party; it's a secret!</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ENG-20260527-244</t>
+          <t>ENG-20260527-343</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>put someone in a tough spot</t>
+          <t>hit the ground running</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4298,29 +4298,29 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>/pʊt ˈsʌmwʌn ɪn ə tʌf spɑːt/</t>
+          <t>/hɪt ðə ɡraʊnd ˈrʌnɪŋ/</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>~를 곤란한 상황에 처하게 하다.</t>
+          <t>즉시 활발하게 일을 시작하다, 빠른 속도로 진행하다</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>AI tools like Mythos will make it harder for people like her to compete.</t>
+          <t>Booming AI chip demand helps create two new $1tn club members. (New companies hit the ground running.)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>His unexpected resignation put the team in a tough spot right before the deadline.</t>
+          <t>Our new marketing intern hit the ground running and quickly became an invaluable part of the team.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ENG-20260527-245</t>
+          <t>ENG-20260527-344</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>keep someone in the loop</t>
+          <t>go with the flow</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4345,29 +4345,29 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>/kiːp ˈsʌmwʌn ɪn ðə luːp/</t>
+          <t>/ɡoʊ wɪθ ðə floʊ/</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>~에게 계속해서 상황을 알려주다, 정보 공유를 유지하다.</t>
+          <t>흐름에 따르다, 순리에 맡기다</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>their name is being kept secret by a disciplinary panel. (inspired by context of keeping information)</t>
+          <t>Phoebe: Oh, I'm sorry, oh, I just, I thought we could have them whipped. (Monica doesn't go with the flow easily.)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Make sure to keep me in the loop about any developments on the project.</t>
+          <t>My travel plans are flexible; I'll just go with the flow and see where the journey takes me.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ENG-20260527-246</t>
+          <t>ENG-20260527-345</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4382,39 +4382,39 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>raise concerns</t>
+          <t>bite the bullet</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>/reɪz kənˈsɜrnz/</t>
+          <t>/baɪt ðə ˈbʊlɪt/</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>우려를 제기하다.</t>
+          <t>어려움을 감수하다, 이를 악물고 참다</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Farmers' warning as milk prices fall below cost</t>
+          <t>Energy bills to rise for millions as impact of Iran war hits. (People will have to bite the bullet.)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>The new safety report raised concerns among employees.</t>
+          <t>I really don't want to work extra hours, but I'll have to bite the bullet to finish this project on time.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ENG-20260527-247</t>
+          <t>ENG-20260527-346</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4424,44 +4424,44 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>take action</t>
+          <t>break a leg</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>/teɪk ˈækʃən/</t>
+          <t>/breɪk ə lɛɡ/</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>조치를 취하다.</t>
+          <t>행운을 빌다 (특히 공연 전에)</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>ECB 'will do what is necessary' to tame inflation</t>
+          <t>Ross: Ok, ok, here we go. (Someone might wish him 'break a leg' before his 'performance' for the baby.)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>We need to take action immediately to address the environmental crisis.</t>
+          <t>You have your big presentation today? Break a leg!</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ENG-20260527-248</t>
+          <t>ENG-20260527-347</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>come to light</t>
+          <t>cost an arm and a leg</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4486,29 +4486,29 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>/kʌm tuː laɪt/</t>
+          <t>/kɔst æn ɑrm ənd ə lɛɡ/</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>밝혀지다, 드러나다.</t>
+          <t>매우 비싸다, 엄청난 비용이 들다</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>The commander leading the national police inquiry says the size of the investigation team would need to double</t>
+          <t>Ferrari shares slump after it unveils first fully electric car. (The new car likely costs an arm and a leg.)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>More details about the scandal are expected to come to light next week.</t>
+          <t>I'd love to buy a house in this neighborhood, but it would cost an arm and a leg.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ENG-20260527-249</t>
+          <t>ENG-20260527-348</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4518,44 +4518,44 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>fall short of expectations</t>
+          <t>get something off one's chest</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>/fɔːl ʃɔːrt ʌv ˌɛkspɛkˈteɪʃənz/</t>
+          <t>/ɡɛt ˈsʌmθɪŋ ɔf wʌnz tʃɛst/</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>기대에 미치지 못하다.</t>
+          <t>마음속의 고민을 털어놓다</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Ferrari shares slump after it unveils first fully electric car</t>
+          <t>Ross: I can't do this. Uh, this is too weird. I feel stupid. (He wants to get this off his chest.)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>The company's latest product launch fell short of market expectations.</t>
+          <t>I've been worried about this for days; I need to get it off my chest.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ENG-20260527-250</t>
+          <t>ENG-20260527-349</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4565,44 +4565,44 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>gain traction</t>
+          <t>let the cat out of the bag</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>/ɡeɪn ˈtrækʃən/</t>
+          <t>/lɛt ðə kæt aʊt ʌv ðə bæɡ/</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>주목/지지를 얻다, 추진력을 얻다.</t>
+          <t>비밀을 누설하다, 폭로하다</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>AI boom lifts South Korean chip stocks</t>
+          <t>Chandler: The most unbelievable thing has happened. Underdog has just gotten away. (He let the cat out of the bag about the balloon incident.)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>The new political movement is starting to gain traction among young voters.</t>
+          <t>We were planning a surprise party for her, but my brother accidentally let the cat out of the bag.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ENG-20260527-251</t>
+          <t>ENG-20260527-350</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4612,12 +4612,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>be on the verge of something</t>
+          <t>lose one's touch</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4627,29 +4627,29 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>/biː ɑn ðə vɜːrdʒ ʌv ˈsʌmθɪŋ/</t>
+          <t>/luːz wʌnz tʌtʃ/</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>막 ~하려고 하다, ~의 직전이다.</t>
+          <t>감각을 잃다, 실력이 떨어지다</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>With SpaceX headed for the public markets next month</t>
+          <t>Joey: Hey, I got one keyhole and about a zillion keys. (He might feel like he's losing his touch at picking locks.)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>The ancient species is now on the verge of extinction.</t>
+          <t>The chef felt he was losing his touch when his famous dish didn't turn out well.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ENG-20260527-252</t>
+          <t>ENG-20260527-351</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>weather the storm</t>
+          <t>stab someone in the back</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4674,29 +4674,29 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>/ˈwɛðər ðə stɔːrm/</t>
+          <t>/stæb ˈsʌmˌwʌn ɪn ðə bæk/</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>어려움을 헤쳐나가다, 위기를 극복하다.</t>
+          <t>~를 배신하다, 뒤통수치다</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Americans are 'entrenched' in financial stress amid debt and price pressures</t>
+          <t>Paxton bests Cornyn in Texas Republican Senate primary after Trump endorsement. (Some might see the endorsement as a stab in the back for Cornyn.)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Small businesses are struggling to weather the storm of the current economic downturn.</t>
+          <t>I can't believe he stabbed me in the back by telling my secret to everyone.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ENG-20260527-253</t>
+          <t>ENG-20260527-352</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>stay afloat</t>
+          <t>the ball is in one's court</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4721,29 +4721,29 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>/steɪ əˈfloʊt/</t>
+          <t>/ðə bɔl ɪz ɪn wʌnz kɔrt/</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>경제적으로 허덕이지 않고 꾸려나가다, 파산하지 않다.</t>
+          <t>(결정이나 행동의) 책임이 ~에게 있다</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Farmers worry more family farms will be sold unless dairy prices rise quickly.</t>
+          <t>Monica: No I don't. Rachel: Yes, you do. When we left, you said, 'got the keys.' (The ball was in Monica's court to find the keys.)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Many companies are cutting costs just to stay afloat during this period.</t>
+          <t>I've made my offer, so now the ball is in your court to accept or decline.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ENG-20260527-254</t>
+          <t>ENG-20260527-353</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4758,39 +4758,39 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>push back a deadline</t>
+          <t>throw in the towel</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>/pʊʃ bæk ə ˈdɛdlaɪn/</t>
+          <t>/θroʊ ɪn ðə ˈtaʊəl/</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>마감 기한을 연기하다.</t>
+          <t>포기하다, 항복하다</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Post Office investigation could be delayed by five years</t>
+          <t>Farmers' warning as milk prices fall below cost. (Some farmers might be forced to throw in the towel.)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>We had to push back the deadline for project submissions due to unforeseen issues.</t>
+          <t>After several failed attempts, he was ready to throw in the towel, but his coach encouraged him to keep going.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ENG-20260527-255</t>
+          <t>ENG-20260527-354</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4805,39 +4805,39 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>brush something off</t>
+          <t>under the weather</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>/brʌʃ ˈsʌmθɪŋ ɔːf/</t>
+          <t>/ˈʌndər ðə ˈwɛðər/</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>(중요하지 않다고 생각하고) ~를 무시하다, 떨쳐버리다.</t>
+          <t>몸이 안 좋다, 약간 아프다</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Yeah, it's no big deal.</t>
+          <t>Ross: I feel stupid. (He might also feel a bit under the weather from the stress.)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>She tried to brush off the criticism, but it clearly affected her.</t>
+          <t>I'm feeling a bit under the weather today, so I might go home early.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ENG-20260527-256</t>
+          <t>ENG-20260527-355</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>get cold feet</t>
+          <t>back to square one</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4862,29 +4862,29 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>/ɡɛt koʊld fiːt/</t>
+          <t>/bæk tuː skwɛər wʌn/</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>겁을 먹다, 망설이다.</t>
+          <t>원점으로 돌아가다, 처음부터 다시 시작하다</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Chandler: I - I don't think I can.</t>
+          <t>Joey: Nope, not that one. (If none of the keys work, they're back to square one.)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>He was planning to propose, but he suddenly got cold feet.</t>
+          <t>Our entire experiment failed, so we're back to square one with our research.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ENG-20260527-257</t>
+          <t>ENG-20260527-356</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>be on the same page</t>
+          <t>beat around the bush</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4909,29 +4909,29 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>/biː ɑn ðə seɪm peɪʤ/</t>
+          <t>/bit əˈraʊnd ðə bʊʃ/</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>같은 생각을 하다, 의견이 일치하다.</t>
+          <t>빙빙 돌려 말하다, 요점을 피하다</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>I guess you're right.</t>
+          <t>Ross: Ok, where am I talking to, here? I mean, uh, well, there is one way that seems to offer a certain acoustical advantage, but... (Ross is beating around the bush.)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Before we proceed, let's ensure everyone is on the same page regarding the project goals.</t>
+          <t>Stop beating around the bush and just tell me what you want to say.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ENG-20260527-258</t>
+          <t>ENG-20260527-357</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>read between the lines</t>
+          <t>bless someone's heart</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4956,29 +4956,29 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>/riːd bɪˈtwiːn ðə laɪnz/</t>
+          <t>/blɛs ˈsʌmˌwʌnz hɑrt/</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>속뜻을 파악하다, 숨겨진 의미를 읽어내다.</t>
+          <t>(남을 동정하거나 살짝 비꼬는 의미로) 안쓰럽네, 착한 심성 가진 사람</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>I lost it. To drugs. (Implied more than said)</t>
+          <t>Phoebe: Yeah, but did they have to shoot him down? I mean, that was just mean. (She might say 'bless their hearts' to the people who shot down the balloon.)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Her email was vague, but if you read between the lines, she wasn't happy.</t>
+          <t>Bless her heart, she tried her best, even though she clearly had no idea what she was doing.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ENG-20260527-259</t>
+          <t>ENG-20260527-358</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>get a grip</t>
+          <t>burn the midnight oil</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5003,29 +5003,29 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>/ɡɛt ə ɡrɪp/</t>
+          <t>/bɜrn ðə ˈmɪdˌnaɪt ɔɪl/</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>정신 차리다, 자제하다.</t>
+          <t>밤늦게까지 일하다, 밤샘하다</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Now, come on, come on, Steve.</t>
+          <t>The Post Office investigation team would need to double in order to meet its current timeline. (They might have to burn the midnight oil.)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>You're panicking; just get a grip and think clearly.</t>
+          <t>I had to burn the midnight oil to finish my report before the deadline.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ENG-20260527-260</t>
+          <t>ENG-20260527-359</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5040,39 +5040,39 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>run into someone</t>
+          <t>can't make heads or tails of</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>/rʌn ˈɪntuː ˈsʌmwʌn/</t>
+          <t>/kænt meɪk hɛdz ɔr teɪlz ʌv/</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>~를 우연히 만나다.</t>
+          <t>~을 도무지 이해할 수 없다</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Ross is just stood up somewhere at a restaurant all alone.</t>
+          <t>Ross: And you have no idea what I'm saying, because, let's face it, you're a fetus. (The fetus can't make heads or tails of what Ross is saying.)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>I ran into an old friend from high school at the grocery store yesterday.</t>
+          <t>I've read these instructions three times, but I still can't make heads or tails of them.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ENG-20260527-261</t>
+          <t>ENG-20260527-360</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5087,32 +5087,79 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>be out of one's league</t>
+          <t>chew someone out</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
+          <t>phrasal verb</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>/tʃuː ˈsʌmˌwʌn aʊt/</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>~를 호되게 꾸짖다, 야단치다</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Monica: (angry) Joey! (She's about to chew him out for being slow with the keys.)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>My boss chewed me out for being late to the important meeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ENG-20260527-361</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>come clean</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
           <t>idiom</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>/bi aʊt əv wʌnz liːɡ/</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>(연애, 능력, 지위 등이) 너무 뛰어나 감히 넘볼 수 없는/수준이 훨씬 높은</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Oh, come on, you're way out of my league.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>She's so smart and accomplished; I feel like I'm completely out of her league.</t>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>/kʌm klin/</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>솔직하게 털어놓다, 고백하다</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Rachel: I swear you said you had the keys. Monica: But I didn't. (One of them needs to come clean about the keys.)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>After weeks of hiding it, he finally decided to come clean about breaking the vase.</t>
         </is>
       </c>
     </row>

--- a/data/02_Daily_Sheets/Expressions_2026-05-27.xlsx
+++ b/data/02_Daily_Sheets/Expressions_2026-05-27.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ENG-20260527-262</t>
+          <t>ENG-20260527-362</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -476,44 +476,44 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>hit a milestone</t>
+          <t>push back against</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>/hɪt ə ˈmaɪlˌstoʊn/</t>
+          <t>/pʊʃ bæk əˈɡɛnst/</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>중요한 이정표나 목표를 달성하다</t>
+          <t>반대하거나 저항하다, 반발하다</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SK Hynix hits $1 trillion valuation as AI boom lifts South Korean chip stocks. This company certainly hit a milestone.</t>
+          <t>Former BP Chairman Albert Manifold has pushed back against accusations over his conduct following his shock departure.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Our startup just hit a major milestone by securing Series B funding.</t>
+          <t>The employees decided to push back against the new policy regarding remote work.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ENG-20260527-263</t>
+          <t>ENG-20260527-363</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>send stocks soaring</t>
+          <t>ink a deal</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -538,29 +538,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>/sɛnd stɑks ˈsɔrɪŋ/</t>
+          <t>/ɪŋk ə diːl/</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>주가를 급등시키다</t>
+          <t>계약에 서명하다, 거래를 성사시키다</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The AI boom lifts South Korean chip stocks, sending them soaring to new heights.</t>
+          <t>Everyone is speculating if SpaceX and Tesla will ink a deal for a potential tie-up soon.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Positive earnings reports sent the company's stocks soaring this morning.</t>
+          <t>The startup is close to inking a deal with a major investor.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ENG-20260527-264</t>
+          <t>ENG-20260527-364</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -575,39 +575,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>top a record</t>
+          <t>come out in force</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>/tɑp ə ˈrɛkərd/</t>
+          <t>/kʌm aʊt ɪn fɔːrs/</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>기록을 경신하다, 최고치를 넘다</t>
+          <t>많은 수가 집결하다, 대거 나타나다</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>South Korea's SK Hynix and U.S. chip firm Micron become the latest companies to top $1 trillion in market capitalization as the AI rally resumes.</t>
+          <t>After the Trump endorsement, voters were expected to come out in force for Paxton.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>The latest sales figures show that we've topped a record in quarterly revenue.</t>
+          <t>Despite the bad weather, fans came out in force to support their favorite team.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ENG-20260527-265</t>
+          <t>ENG-20260527-365</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>do what it takes</t>
+          <t>throw one's weight behind</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -632,29 +632,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>/du wʌt ɪt teɪks/</t>
+          <t>/θroʊ wʌnz weɪt bɪˈhaɪnd/</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>필요한 모든 조치를 취하다, 수단과 방법을 가리지 않다</t>
+          <t>누군가나 무언가를 적극적으로 지지하고 영향력을 행사하다</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ECB 'will do what is necessary' to tame inflation, meaning they will do what it takes.</t>
+          <t>President Trump threw his weight behind Texas Attorney General Ken Paxton, impacting the primary results.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>We'll do what it takes to meet the project deadline, even if it means working overtime.</t>
+          <t>The CEO decided to throw her weight behind the new sustainability initiative.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ENG-20260527-266</t>
+          <t>ENG-20260527-366</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -664,44 +664,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>dash hopes</t>
+          <t>beef up</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>/dæʃ hoʊps/</t>
+          <t>/biːf ʌp/</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>기대를 좌절시키다, 희망을 꺾다</t>
+          <t>강화하다, 보강하다</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Changing immigration rules and a weak hiring market dash hopes for international students seeking U.S. jobs.</t>
+          <t>Russia needs to beef up its anti-drone defense systems to counter attacks.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>The unexpected downturn in the market dashed the hopes of many aspiring entrepreneurs.</t>
+          <t>The company plans to beef up its cybersecurity measures after a recent data breach.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ENG-20260527-267</t>
+          <t>ENG-20260527-367</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -716,39 +716,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>be behind something</t>
+          <t>take a nosedive</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>/bi bɪˈhaɪnd ˈsʌmθɪŋ/</t>
+          <t>/teɪk ə ˈnoʊzdaɪv/</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>어떤 일의 원인이 되다, 배후에 있다</t>
+          <t>급락하다, 폭락하다</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>'Bullying' and 'overbearing' behaviour behind abrupt BP chairman removal. That's what was behind his dismissal.</t>
+          <t>Ferrari shares took a nosedive after it unveiled its first fully electric car to a divided public.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>We need to find out who is really behind these rumors.</t>
+          <t>After the scandal, the politician's approval ratings took a nosedive.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ENG-20260527-268</t>
+          <t>ENG-20260527-368</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -758,44 +758,44 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>get away</t>
+          <t>hit a record high</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>/ɡɛt əˈweɪ/</t>
+          <t>/hɪt ə ˈrɛkərd haɪ/</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>도망치다, 빠져나가다</t>
+          <t>최고 기록을 경신하다</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>The most unbelievable thing has happened. Underdog has just gotten away.</t>
+          <t>SK Hynix shares hit a record high, pushing its valuation above $1 trillion.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>The suspect managed to get away from the police after a brief chase.</t>
+          <t>Oil prices hit a record high last month, causing concerns for consumers.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ENG-20260527-269</t>
+          <t>ENG-20260527-369</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -805,44 +805,44 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>be all over the news</t>
+          <t>take off</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>/bi ɔl ˈoʊvər ðə nuːz/</t>
+          <t>/teɪk ɒf/</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>뉴스를 도배하다, 온통 뉴스에 나오다</t>
+          <t>갑자기 성공하다, 인기를 얻다; (주식 등이) 급등하다</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Of course the balloon. It's all over the news.</t>
+          <t>The AI rally resumed, and many tech stocks started to take off again.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>The celebrity scandal was all over the news for weeks.</t>
+          <t>Her new business really started to take off after a successful marketing campaign.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ENG-20260527-270</t>
+          <t>ENG-20260527-370</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -852,44 +852,44 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>break free</t>
+          <t>feel the pinch</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>/breɪk friː/</t>
+          <t>/fiːl ðə pɪntʃ/</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>탈출하다, 벗어나다</t>
+          <t>재정적 어려움을 느끼다, 궁핍함을 겪다</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Right before he reached Macy's, he broke free and was spotted flying over Washington Square Park.</t>
+          <t>Americans are feeling the pinch as inflation and high debt levels continue to cause financial anxiety.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>The wild animal managed to break free from its enclosure.</t>
+          <t>Many families are starting to feel the pinch with the rising cost of living.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ENG-20260527-271</t>
+          <t>ENG-20260527-371</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -899,44 +899,44 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>let loose</t>
+          <t>tighten one's belt</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>/lɛt luːs/</t>
+          <t>/ˈtaɪtn wʌnz bɛlt/</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>(묶인 것을) 풀다; (감정이나 행동을) 마음껏 발산하다</t>
+          <t>허리띠를 졸라매다, 지출을 줄이다</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Come on. An 80-foot inflatable dog let loose over the city. How often does that happen?</t>
+          <t>With energy bills set to rise, many households will have to tighten their belts.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>After a stressful week, I just want to let loose and dance.</t>
+          <t>Due to the economic downturn, we'll all have to tighten our belts for a while.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ENG-20260527-272</t>
+          <t>ENG-20260527-372</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>crouch down</t>
+          <t>drag on</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -961,29 +961,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>/kraʊtʃ daʊn/</t>
+          <t>/dræɡ ɒn/</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>웅크리다, 쭈그리고 앉다</t>
+          <t>지루하게 오래 계속되다, 지연되다</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Ok, ok, here we go. (he crouches down near her stomach) Ok, where am I talking to, here?</t>
+          <t>The Post Office investigation could drag on for another five years if resources aren't increased.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>The photographer had to crouch down to get a good shot of the flowers.</t>
+          <t>The negotiations have been dragging on for weeks without a clear resolution.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ENG-20260527-273</t>
+          <t>ENG-20260527-373</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -993,44 +993,44 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>aim for</t>
+          <t>put on hold</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>/eɪm fɔr/</t>
+          <t>/pʊt ɒn hoʊld/</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>~을 목표로 하다, 겨냥하다</t>
+          <t>보류하다, 연기하다</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Just aim for the bump.</t>
+          <t>The Post Office investigation might be put on hold due to a lack of resources.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Always aim for progress, not perfection.</t>
+          <t>We've decided to put the new project on hold until next quarter.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ENG-20260527-274</t>
+          <t>ENG-20260527-374</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>here goes</t>
+          <t>stay ahead of the curve</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1055,29 +1055,29 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>/hɪər ɡoʊz/</t>
+          <t>/steɪ əˈhɛd ɒv ðə kɜːrv/</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>자, 시작한다 (새로운/어려운 일을 시작할 때 쓰는 말)</t>
+          <t>트렌드나 경쟁에서 앞서나가다, 시대를 앞서가다</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Ok, ok, ok, ok, here goes. You know, I, you know, can't do this.</t>
+          <t>Chompie warns that ethical hackers need to stay ahead of the curve as AI tools evolve.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>I'm about to give my presentation. Here goes nothing!</t>
+          <t>To remain competitive, companies must constantly innovate and stay ahead of the curve.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ENG-20260527-275</t>
+          <t>ENG-20260527-375</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>all over the place</t>
+          <t>up one's game</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1102,29 +1102,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>/ɔl ˈoʊvər ðə pleɪs/</t>
+          <t>/ʌp wʌnz ɡeɪm/</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>여기저기 흩어져 있는; 두서없는, 엉망진창인</t>
+          <t>실력을 향상시키다, 더 잘하다</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>I loved the moment when you first saw the giant dog shadow all over the park.</t>
+          <t>The rise of AI tools means human hackers will have to up their game to compete.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>My thoughts were all over the place after hearing the shocking news.</t>
+          <t>If you want that promotion, you'll really need to up your game in sales.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ENG-20260527-276</t>
+          <t>ENG-20260527-376</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>shoot down</t>
+          <t>crack down on</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1149,29 +1149,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>/ʃuːt daʊn/</t>
+          <t>/kræk daʊn ɒn/</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>(생각, 제안 등을) 거절하다, 묵살하다</t>
+          <t>단속하다, 엄격하게 규제하다</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Yeah, but did they have to shoot him down? I mean, that was just mean.</t>
+          <t>The advertising watchdog decided to crack down on Instagram betting ads featuring footballers.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>My boss tends to shoot down any new ideas without even considering them.</t>
+          <t>The government is cracking down on tax evasion to boost revenue.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ENG-20260527-277</t>
+          <t>ENG-20260527-377</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1181,44 +1181,44 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>right about now</t>
+          <t>iron out</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>/raɪt əˈbaʊt naʊ/</t>
+          <t>/ˈaɪərn aʊt/</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>바로 지금쯤</t>
+          <t>(문제, 오해 등을) 해결하다, 해소하다</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Ok, right about now the turkey should be crispy on the outside, juicy on the inside.</t>
+          <t>Before the merger can proceed, both companies need to iron out a few legal details.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>The delivery should arrive right about now, so let's get ready.</t>
+          <t>Let's meet tomorrow to iron out the final details of the proposal.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ENG-20260527-278</t>
+          <t>ENG-20260527-378</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1228,44 +1228,44 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>pick a major</t>
+          <t>hammer out</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>/pɪk ə ˈmeɪʤər/</t>
+          <t>/ˈhæmər aʊt/</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>전공을 선택하다</t>
+          <t>협의나 논의를 거쳐 (합의, 계획 등을) 힘들게 도출해내다</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>And everyone's telling me, you gotta pick a major, you gotta pick a major.</t>
+          <t>The two sides spent all night trying to hammer out a compromise on the budget.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>It's difficult for many high school students to pick a major before they even start college.</t>
+          <t>They finally hammered out a new contract after weeks of negotiation.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ENG-20260527-279</t>
+          <t>ENG-20260527-379</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1275,44 +1275,44 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>on a dare</t>
+          <t>call out</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>/ɑn ə dɛr/</t>
+          <t>/kɔːl aʊt/</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>내기/도전으로, 장난 삼아</t>
+          <t>비판하다, 잘못을 지적하다; (도움을 요청하며) 부르다</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>So, on a dare, I picked paleontology.</t>
+          <t>The employee decided to call out the bullying behavior of their superior.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>He ate the entire super spicy chili, just on a dare from his friends.</t>
+          <t>It's important to call out discriminatory remarks when you hear them.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ENG-20260527-280</t>
+          <t>ENG-20260527-380</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1322,44 +1322,44 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>have no idea</t>
+          <t>opt out of</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>/hæv noʊ aɪˈdiːə/</t>
+          <t>/ɒpt aʊt ɒv/</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>전혀 모르다</t>
+          <t>선택하지 않다, ~에서 빠져나가다</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>And you have no idea what I'm saying, because, let's face it, you're a fetus.</t>
+          <t>Many students are choosing to opt out of the traditional university system for vocational training.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>I have no idea how to fix this computer problem.</t>
+          <t>Employees can opt out of the company's health insurance plan if they have their own.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ENG-20260527-281</t>
+          <t>ENG-20260527-381</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1369,44 +1369,44 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>let's face it</t>
+          <t>phase out</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>/lɛts feɪs ɪt/</t>
+          <t>/feɪz aʊt/</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>솔직히 말해서, 현실을 직시하자면</t>
+          <t>단계적으로 중단하다, 폐지하다</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>And you have no idea what I'm saying, because, let's face it, you're a fetus.</t>
+          <t>The company plans to phase out its old product line to make way for new innovations.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Let's face it, we're not going to finish this project by tonight.</t>
+          <t>The government is trying to phase out the use of plastic bags over the next few years.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ENG-20260527-282</t>
+          <t>ENG-20260527-382</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>sing to</t>
+          <t>reel in</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1431,29 +1431,29 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>/sɪŋ tuː/</t>
+          <t>/riːl ɪn/</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>~에게 노래를 불러주다</t>
+          <t>유인하여 끌어들이다 (특히 고객, 투자자 등)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Look, you don't have to talk to it. You can sing to it if you want.</t>
+          <t>The new marketing campaign aims to reel in more subscribers to our streaming service.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>My grandmother used to sing to me every night before bed.</t>
+          <t>They used celebrity endorsements to reel in a younger demographic.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ENG-20260527-283</t>
+          <t>ENG-20260527-383</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1463,44 +1463,44 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>get looks from</t>
+          <t>weigh in</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>/ɡɛt lʊks frʌm/</t>
+          <t>/weɪ ɪn/</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>~에게 시선을 받다, 주목받다</t>
+          <t>논쟁이나 토론에 의견을 보태다, 개입하다</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Here we come, walkin' down the street, get the funniest looks from, everyone we meet.</t>
+          <t>Several industry experts weighed in on the potential SpaceX-Tesla merger chatter.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>She gets a lot of admiring looks from strangers when she wears that dress.</t>
+          <t>The CEO decided to weigh in on the controversial decision during the board meeting.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ENG-20260527-284</t>
+          <t>ENG-20260527-384</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1510,12 +1510,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>keep doing something</t>
+          <t>hold off on</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1525,29 +1525,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>/kiːp ˈduːɪŋ ˈsʌmθɪŋ/</t>
+          <t>/hoʊld ɒf ɒn/</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>계속 ~하다</t>
+          <t>~을 보류하다, ~을 미루다</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Keep singing! Keep singing!</t>
+          <t>Let's hold off on making a final decision until we have all the information.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>If you keep practicing, you'll definitely improve your skills.</t>
+          <t>They decided to hold off on their travel plans until the pandemic situation improves.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ENG-20260527-285</t>
+          <t>ENG-20260527-385</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>come out</t>
+          <t>step down</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1572,29 +1572,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>/kʌm aʊt/</t>
+          <t>/stɛp daʊn/</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>나오다, 드러나다; (영화, 책 등이) 출시되다</t>
+          <t>사임하다, 물러나다</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>When you come out I'll buy you a bagel, and then we'll go to the zoo.</t>
+          <t>The chairman was forced to step down after accusations of misconduct.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>The results of the election will come out sometime next week.</t>
+          <t>She announced her decision to step down as CEO at the end of the year.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ENG-20260527-286</t>
+          <t>ENG-20260527-386</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1604,44 +1604,44 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>do the math</t>
+          <t>step up</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>/duː ðə mæθ/</t>
+          <t>/stɛp ʌp/</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>계산해봐, 따져봐</t>
+          <t>더 많은 책임을 맡다, 한 단계 올라서다; (노력 등을) 강화하다</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Hey, I got one keyhole and about a zillion keys. You do the math.</t>
+          <t>In the absence of the manager, someone needs to step up and lead the team.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>If we only have 30 minutes for five presentations, do the math; each person gets six minutes.</t>
+          <t>We need to step up our customer service to retain our clients.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ENG-20260527-287</t>
+          <t>ENG-20260527-387</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1651,44 +1651,44 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>for an emergency</t>
+          <t>back out of</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>/fɔr æn ɪˈmɜrʤənsi/</t>
+          <t>/bæk aʊt ɒv/</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>비상시를 대비하여</t>
+          <t>약속이나 계약을 취소하다, 손을 떼다</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(sarcastic) For an emergency just like this.</t>
+          <t>He tried to back out of the deal at the last minute, but the contract was binding.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Always keep a fully charged power bank for an emergency.</t>
+          <t>The investor decided to back out of the agreement due to new market conditions.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ENG-20260527-288</t>
+          <t>ENG-20260527-388</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1698,44 +1698,44 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>if it wasn't for</t>
+          <t>follow through on</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>/ɪf ɪt wɑzənt fɔr/</t>
+          <t>/ˈfɒloʊ θruː ɒn/</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>~가 아니었더라면</t>
+          <t>약속, 계획 등을 이행하다, 끝까지 실행하다</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>If it wasn't for you and your stupid balloon, I would be on a plane watching a woman do this right now.</t>
+          <t>It's important to follow through on your commitments to build trust with clients.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>If it wasn't for my alarm clock, I would have overslept and missed my flight.</t>
+          <t>She always follows through on her promises, which makes her a reliable leader.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ENG-20260527-289</t>
+          <t>ENG-20260527-389</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>swear by</t>
+          <t>branch out</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1760,29 +1760,29 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>/swɛər baɪ/</t>
+          <t>/bræntʃ aʊt/</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>~을 맹신하다, ~의 효능/효과를 믿다</t>
+          <t>새로운 분야로 진출하다, 사업을 확장하다</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Monica: I swear you said you had the keys. Rachel: No, I didn't. (inspired by 'swear you said')</t>
+          <t>The tech company decided to branch out into the clean energy sector.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>My mom swears by this natural remedy for colds; she says it always works.</t>
+          <t>After years in finance, she decided to branch out and start her own consulting firm.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ENG-20260527-290</t>
+          <t>ENG-20260527-390</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1792,44 +1792,44 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>aside from the fact that</t>
+          <t>map out</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>/əˈsaɪd frʌm ðə fæk ðæt/</t>
+          <t>/mæp aʊt/</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>~라는 사실을 제외하면</t>
+          <t>자세하게 계획을 세우다, 설계하다</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Aside from the fact that you said you had them?</t>
+          <t>We need to map out a strategy for dealing with the increased competition.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Aside from the fact that it's raining, it's a perfect day for a picnic.</t>
+          <t>Before starting the trip, they mapped out their entire route and planned for all contingencies.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ENG-20260527-291</t>
+          <t>ENG-20260527-391</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>hang out</t>
+          <t>zero in on</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1854,29 +1854,29 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>/hæŋ aʊt/</t>
+          <t>/ˈzɪəroʊ ɪn ɒn/</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>어울려 놀다, 시간을 보내다</t>
+          <t>~에 집중하다, ~을 목표로 삼다</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Ross: Does it always, uh--? (A group of friends often hang out together)</t>
+          <t>The investigation will zero in on the specific details of the financial transactions.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Do you want to hang out at the coffee shop later?</t>
+          <t>The detective managed to zero in on the key suspect after reviewing all the evidence.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ENG-20260527-292</t>
+          <t>ENG-20260527-392</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>catch up</t>
+          <t>kick off</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1901,29 +1901,29 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>/kætʃ ʌp/</t>
+          <t>/kɪk ɒf/</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>밀린 이야기를 나누다; (지연된 일을) 따라잡다</t>
+          <t>시작하다, 개시하다</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Monica: Ok, right about now the turkey should be crispy on the outside. (Friends often catch up on each other's lives)</t>
+          <t>The conference will kick off with a keynote speech from the CEO.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Let's grab lunch next week and catch up.</t>
+          <t>Let's kick off the meeting by reviewing the agenda.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ENG-20260527-293</t>
+          <t>ENG-20260527-393</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>run into</t>
+          <t>wind down</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1948,29 +1948,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>/rʌn ˈɪntuː/</t>
+          <t>/waɪnd daʊn/</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>우연히 마주치다</t>
+          <t>서서히 끝나다, 마무리하다; 휴식을 취하다</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Rachel: I loved the moment when you first saw the giant dog shadow. (It's common to run into people in the city)</t>
+          <t>The event will wind down around 5 PM with a networking reception.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>I ran into my old high school teacher at the grocery store yesterday.</t>
+          <t>After a busy day, I like to wind down by reading a book.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ENG-20260527-294</t>
+          <t>ENG-20260527-394</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>mess up</t>
+          <t>burn out</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1995,29 +1995,29 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>/mɛs ʌp/</t>
+          <t>/bɜːrn aʊt/</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>망치다, 실수하다</t>
+          <t>(과로 등으로) 기진맥진하다, 소진되다</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Phoebe: Oh, I'm sorry, oh, I just, I thought we could have them whipped. (Phoebe felt like she messed up the potatoes)</t>
+          <t>Working 80 hours a week can quickly lead to burnout and stress.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>I really messed up my presentation; I forgot half of what I wanted to say.</t>
+          <t>She decided to take a sabbatical to avoid burning out from her demanding job.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ENG-20260527-295</t>
+          <t>ENG-20260527-395</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>call off</t>
+          <t>cash in on</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2042,29 +2042,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>/kɔl ɔf/</t>
+          <t>/kæʃ ɪn ɒn/</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>취소하다</t>
+          <t>~을 이용해 이득을 얻다, ~로 돈을 벌다</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Chandler: The most unbelievable thing has happened. (Sometimes plans get called off unexpectedly)</t>
+          <t>Many companies are trying to cash in on the growing demand for AI technology.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>They had to call off the outdoor concert due to heavy rain.</t>
+          <t>They hoped to cash in on the holiday season by offering special discounts.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ENG-20260527-296</t>
+          <t>ENG-20260527-396</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>turn down</t>
+          <t>dig in</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2089,29 +2089,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>/tɜrn daʊn/</t>
+          <t>/dɪɡ ɪn/</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>거절하다; (소리, 불빛 등을) 줄이다</t>
+          <t>열심히 먹기 시작하다; 굳게 버티다, 고수하다</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Carol: So don't do it, it's fine. You don't have to do it just because Susan does it. (Ross wanted to turn down the offer to sing)</t>
+          <t>When the food arrived, everyone started to dig in with enthusiasm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>I had to turn down the job offer because it wasn't a good fit for me.</t>
+          <t>Despite the opposition, the politician dug in and refused to change his stance.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ENG-20260527-297</t>
+          <t>ENG-20260527-397</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2121,12 +2121,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>go through</t>
+          <t>get ahead</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2136,29 +2136,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>/ɡoʊ θruː/</t>
+          <t>/ɡɛt əˈhɛd/</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>겪다, 경험하다; (서류 등을) 검토하다</t>
+          <t>성공하다, 앞서나가다</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Ross: And everyone's telling me, you gotta pick a major. (He's going through a lot of pressure)</t>
+          <t>Many international students find it harder to get ahead in the US job market.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>She's going through a difficult time after losing her job.</t>
+          <t>To get ahead in this industry, you need to be constantly learning new skills.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ENG-20260527-298</t>
+          <t>ENG-20260527-398</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>pull off</t>
+          <t>get by</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2183,29 +2183,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>/pʊl ɔf/</t>
+          <t>/ɡɛt baɪ/</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>성공적으로 해내다, 해치우다</t>
+          <t>그럭저럭 살아가다, 근근이 생활하다</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Joey: Hey, I got one keyhole and about a zillion keys. You do the math. (Pulling off opening the door with so many keys would be impressive)</t>
+          <t>With prices rising, it's becoming harder for families to get by on a single income.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>I can't believe they managed to pull off such a complex event with so little planning.</t>
+          <t>I don't earn much, but I manage to get by with careful budgeting.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ENG-20260527-299</t>
+          <t>ENG-20260527-399</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>get over</t>
+          <t>give in</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2230,29 +2230,29 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>/ɡɛt ˈoʊvər/</t>
+          <t>/ɡɪv ɪn/</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>(문제, 어려움, 병 등을) 극복하다; (상대방에 대한 감정을) 잊다</t>
+          <t>양보하다, 굴복하다</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Phoebe: Yeah, but did they have to shoot him down? I mean, that was just mean. (It's hard to get over mean actions)</t>
+          <t>After hours of debate, the opposing party finally gave in and accepted the proposal.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>It took her a long time to get over the breakup.</t>
+          <t>My kids kept asking for ice cream until I finally gave in.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ENG-20260527-300</t>
+          <t>ENG-20260527-400</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>look up to</t>
+          <t>give up on</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2277,29 +2277,29 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>/lʊk ʌp tuː/</t>
+          <t>/ɡɪv ʌp ɒn/</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>~을 존경하다, 우러러보다</t>
+          <t>~을 포기하다, ~에 대한 희망을 버리다</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Susan: I felt it! Ross: (singin) Hey, hey, I'm your daddy. (A child might look up to their father)</t>
+          <t>Don't give up on your American dream, even if the job market is tough.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Many young athletes look up to professional sports stars as role models.</t>
+          <t>We can't give up on finding a solution to this problem, no matter how difficult it seems.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ENG-20260527-301</t>
+          <t>ENG-20260527-401</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>put off</t>
+          <t>grow on</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2324,29 +2324,29 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>/pʊt ɔf/</t>
+          <t>/ɡroʊ ɒn/</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>연기하다, 미루다; ~에게 불쾌감을 주다</t>
+          <t>점점 더 좋아지다, 마음에 들게 되다</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Monica: Can you go any faster with that? (Joey was putting off finding the right key)</t>
+          <t>At first, I didn't like the new office design, but it's starting to grow on me.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Don't put off your homework until the last minute.</t>
+          <t>The new song wasn't my favorite initially, but it really started to grow on me after a few listens.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ENG-20260527-302</t>
+          <t>ENG-20260527-402</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>deal with</t>
+          <t>hand over</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2371,29 +2371,29 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>/dil wɪð/</t>
+          <t>/hænd ˈoʊvər/</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>다루다, 처리하다</t>
+          <t>넘겨주다, 양도하다</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Monica: (panicked) The oven is on. (They needed to deal with the locked door situation)</t>
+          <t>The outgoing CEO will hand over his responsibilities to his successor next month.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>The customer service team is trained to deal with difficult complaints calmly.</t>
+          <t>The company decided to hand over its operations to a local partner in the region.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ENG-20260527-303</t>
+          <t>ENG-20260527-403</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>figure out</t>
+          <t>knock off</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2418,29 +2418,29 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>/ˈfɪɡjər aʊt/</t>
+          <t>/nɒk ɒf/</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>알아내다, 이해하다; 해결하다</t>
+          <t>일을 마치다, 퇴근하다; 가격을 깎다; 빠르게 만들다/생산하다</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Rachel: I swear you said you had the keys. Monica: But I didn't. (They needed to figure out who had the keys)</t>
+          <t>We can probably knock off early if we finish all our tasks by lunchtime.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>I'm trying to figure out how to install this new software.</t>
+          <t>Can you knock off 10% from the price if I buy two items?</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ENG-20260527-304</t>
+          <t>ENG-20260527-404</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>come across</t>
+          <t>lay off</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2465,29 +2465,29 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>/kʌm əˈkrɔs/</t>
+          <t>/leɪ ɒf/</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>우연히 발견하다; ~라는 인상을 주다</t>
+          <t>(직원을) 해고하다, 일시 해고하다</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Phoebe: Oh, I'm sorry, oh, I just, I thought we could have them whipped. (Monica came across as demanding)</t>
+          <t>Due to decreased demand, the factory had to lay off a significant number of workers.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>I came across an old photo album while cleaning the attic.</t>
+          <t>The struggling startup had to lay off a third of its staff to stay afloat.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ENG-20260527-305</t>
+          <t>ENG-20260527-405</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>fall apart</t>
+          <t>let down</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2512,29 +2512,29 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>/fɔl əˈpɑrt/</t>
+          <t>/lɛt daʊn/</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>허물어지다, 무너지다; 붕괴하다</t>
+          <t>실망시키다, 저버리다</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Ross: I can't do this. Uh, this is too weird. I feel stupid. (Ross felt like he was falling apart under pressure)</t>
+          <t>I hope I don't let down my team with my performance in the upcoming presentation.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>After the scandal, the company's reputation started to fall apart.</t>
+          <t>She felt completely let down by her friend who didn't show up.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ENG-20260527-306</t>
+          <t>ENG-20260527-406</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>patch things up</t>
+          <t>live up to</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2559,29 +2559,29 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>/pætʃ θɪŋz ʌp/</t>
+          <t>/lɪv ʌp tuː/</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>관계를 회복하다, 화해하다</t>
+          <t>(기대, 명성 등에) 부응하다, 부합하다</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Rachel: I swear you said you had the keys. Monica: But I didn't. (Monica and Rachel need to patch things up after their argument)</t>
+          <t>The new product needs to live up to the high expectations set by its marketing campaign.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>After their big fight, John and Sarah decided to patch things up.</t>
+          <t>The movie didn't quite live up to the hype, but it was still entertaining.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ENG-20260527-307</t>
+          <t>ENG-20260527-407</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>fill someone in</t>
+          <t>make for</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2606,29 +2606,29 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>/fɪl ˈsʌmˌwʌn ɪn/</t>
+          <t>/meɪk fɔːr/</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>~에게 소식을 전하다, 상황을 알려주다</t>
+          <t>~쪽으로 가다; ~에 도움이 되다, ~을 야기하다</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Chandler: The most unbelievable thing has happened. Underdog has just gotten away. (He's filling them in on the news)</t>
+          <t>The rising prices will make for increased financial stress for many families.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>I missed the meeting, so can you fill me in on what was discussed?</t>
+          <t>A strong team spirit makes for a productive work environment.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ENG-20260527-308</t>
+          <t>ENG-20260527-408</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>nod off</t>
+          <t>make up for</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2653,29 +2653,29 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>/nɑd ɔf/</t>
+          <t>/meɪk ʌp fɔːr/</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>꾸벅꾸벅 졸다</t>
+          <t>~을 만회하다, 보충하다; ~을 보상하다</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Ross: And you have no idea what I'm saying, because, let's face it, you're a fetus. (A fetus would nod off during a long speech)</t>
+          <t>He tried to make up for his mistake by working extra hours over the weekend.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>The lecture was so boring that I kept nodding off in my seat.</t>
+          <t>The free dessert didn't really make up for the terrible service we received.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ENG-20260527-309</t>
+          <t>ENG-20260527-409</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>brush off</t>
+          <t>miss out on</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2700,29 +2700,29 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>/brʌʃ ɔf/</t>
+          <t>/mɪs aʊt ɒn/</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>묵살하다, 무시하다</t>
+          <t>~을 놓치다, ~에 참여하지 못하다</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Phoebe: Yeah, but did they have to shoot him down? (The authorities might brush off public complaints)</t>
+          <t>Don't miss out on the opportunity to invest in these booming AI chip stocks.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>He tried to brush off my concerns, but I insisted on discussing them.</t>
+          <t>I'd hate to miss out on the annual company picnic this year.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ENG-20260527-310</t>
+          <t>ENG-20260527-410</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>talk over</t>
+          <t>pass up</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2747,29 +2747,29 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>/tɔk ˈoʊvər/</t>
+          <t>/pæs ʌp/</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>상의하다, ~에 대해 논의하다</t>
+          <t>~을 거절하다, ~을 놓치다</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Rachel: I swear you said you had the keys. Monica: But I didn't. (They should talk over the key situation calmly)</t>
+          <t>She couldn't pass up the chance to work at such a prestigious company.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Let's talk over the project details before making any final decisions.</t>
+          <t>It's a great opportunity, you shouldn't pass it up.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ENG-20260527-311</t>
+          <t>ENG-20260527-411</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>butt in</t>
+          <t>pick up on</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2794,29 +2794,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>/bʌt ɪn/</t>
+          <t>/pɪk ʌp ɒn/</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>(대화나 일에) 끼어들다, 참견하다</t>
+          <t>~을 알아채다, 눈치채다</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Phoebe: Ooh, ok, that's it. Enough with the keys. No one say keys. (She butted in to stop the argument)</t>
+          <t>He didn't directly say it, but I picked up on the fact that he wasn't happy with the decision.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>It's rude to butt in when other people are talking.</t>
+          <t>She's very observant and always picks up on subtle changes in people's moods.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ENG-20260527-312</t>
+          <t>ENG-20260527-412</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>bail on</t>
+          <t>point out</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2841,29 +2841,29 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>/beɪl ɑn/</t>
+          <t>/pɔɪnt aʊt/</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>(약속, 책임 등을) 저버리다, 바람맞히다</t>
+          <t>지적하다, 언급하다</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Rachel: I can't, I gotta go. (She had to bail on going to the roof)</t>
+          <t>The expert pointed out that the AI rally might not last forever.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>He bailed on our dinner plans at the last minute.</t>
+          <t>The teacher pointed out several errors in my essay.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ENG-20260527-313</t>
+          <t>ENG-20260527-413</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>chicken out</t>
+          <t>read into</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2888,29 +2888,29 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>/ˈʧɪkɪn aʊt/</t>
+          <t>/riːd ˈɪntuː/</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>겁먹고 포기하다, 꽁무니 빼다</t>
+          <t>(숨겨진 의미를) 지나치게 확대 해석하다</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Ross: Ok, ok, ok, ok, here goes. You know, I, you know, can't do this. Uh, this is too weird. I feel stupid. (Ross almost chickened out of talking to Carol's belly)</t>
+          <t>Don't read too much into his comments; he's probably just tired.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>I was going to try skydiving, but I chickened out at the last moment.</t>
+          <t>She tends to read into every little gesture, looking for hidden meanings.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ENG-20260527-314</t>
+          <t>ENG-20260527-414</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>fend off</t>
+          <t>root for</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2935,29 +2935,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>/fɛnd ɔf/</t>
+          <t>/ruːt fɔːr/</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>~을 물리치다, 막아내다</t>
+          <t>~을 응원하다, 지지하다</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>European companies double down on China manufacturing despite EU de-risking push. (Companies need to fend off pressure from EU.)</t>
+          <t>I'm always rooting for the underdog in any competition.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>The politician had to fend off tough questions from reporters during the press conference.</t>
+          <t>Our whole family is rooting for you to win the championship.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ENG-20260527-315</t>
+          <t>ENG-20260527-415</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>pencil in</t>
+          <t>rub off on</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2982,29 +2982,29 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>/ˈpɛnsəl ɪn/</t>
+          <t>/rʌb ɒf ɒn/</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>임시로 일정을 잡다</t>
+          <t>(특성, 습관 등이) ~에게 전염되다, 영향을 주다</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>The Post Office investigation could be delayed by five years, police warn. (They need to pencil in new timelines)</t>
+          <t>Her enthusiasm for the project eventually started to rub off on the rest of the team.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Let's pencil in a meeting for Tuesday afternoon, and I'll confirm with everyone.</t>
+          <t>I hope some of your good study habits rub off on me.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ENG-20260527-316</t>
+          <t>ENG-20260527-416</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>rule out</t>
+          <t>set out</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3029,29 +3029,29 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>/rul aʊt/</t>
+          <t>/sɛt aʊt/</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>배제하다, ~의 가능성을 없애다</t>
+          <t>출발하다; (목표를 가지고) 시작하다; 진술하다, 제시하다</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>The commander leading the national police inquiry needs to rule out other possibilities.</t>
+          <t>The new initiative sets out clear guidelines for ethical AI development.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>The detective couldn't rule out the possibility of foul play.</t>
+          <t>They set out to build the most innovative smartphone on the market.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ENG-20260527-317</t>
+          <t>ENG-20260527-417</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>wear off</t>
+          <t>size up</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3076,29 +3076,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>/wɛər ɔf/</t>
+          <t>/saɪz ʌp/</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>점점 사라지다, 효과가 없어지다</t>
+          <t>평가하다, 상황을 판단하다</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Energy bills to rise for millions as impact of Iran war hits. (The relief of lower prices will wear off)</t>
+          <t>The investors are trying to size up the potential risks of the new venture.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>The initial excitement of the new job started to wear off after a few months.</t>
+          <t>Before making a move, it's always good to size up your opponent.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ENG-20260527-318</t>
+          <t>ENG-20260527-418</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>go back on</t>
+          <t>stand out</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3123,29 +3123,29 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>/ɡoʊ bæk ɑn/</t>
+          <t>/stænd aʊt/</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>(약속, 합의 등을) 어기다, 철회하다</t>
+          <t>눈에 띄다, 두드러지다</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>European companies double down on China manufacturing despite EU de-risking push. (EU feels they go back on agreements)</t>
+          <t>Her unique presentation really made her stand out among the other candidates.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>He's known for always keeping his word and never going back on a promise.</t>
+          <t>To get noticed in a crowded market, your product needs to stand out.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ENG-20260527-319</t>
+          <t>ENG-20260527-419</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3155,44 +3155,44 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>touch base</t>
+          <t>stir up</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>/tʌtʃ beɪs/</t>
+          <t>/stɜːr ʌp/</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>간략히 연락하다, 안부를 묻거나 상황을 확인하다</t>
+          <t>(문제, 감정 등을) 불러일으키다, 자극하다</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>With SpaceX headed for the public markets next month, industry experts and people close to Elon Musk are speculating about a potential tie-up with Tesla. (They need to touch base with Musk's team)</t>
+          <t>His controversial comments stirred up a lot of debate on social media.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Let's touch base next week to discuss the progress of the project.</t>
+          <t>Don't stir up trouble by talking about sensitive topics at the family dinner.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ENG-20260527-320</t>
+          <t>ENG-20260527-420</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3202,44 +3202,44 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>circle back</t>
+          <t>string along</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>/ˈsɜrkəl bæk/</t>
+          <t>/strɪŋ əˈlɒŋ/</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>(나중에) 다시 논의하다, 재론하다</t>
+          <t>~을 속이다, ~을 희망 고문하다</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>The ECB 'will do what is necessary' to tame inflation. (They might need to circle back to their strategies)</t>
+          <t>I feel like they're just stringing me along with promises of a promotion.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>That's a good point, but let's circle back to it after we've covered the main agenda items.</t>
+          <t>She realized her ex-boyfriend was just stringing her along and never intended to get serious.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ENG-20260527-321</t>
+          <t>ENG-20260527-421</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3249,44 +3249,44 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>hit a snag</t>
+          <t>take on</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>/hɪt ə snæɡ/</t>
+          <t>/teɪk ɒn/</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>예상치 못한 문제에 부딪히다</t>
+          <t>책임을 맡다; (도전, 임무 등을) 받아들이다; (직원을) 고용하다</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>The Post Office investigation could be delayed by five years, police warn. (The investigation hit a snag)</t>
+          <t>She was hesitant to take on such a challenging role, but she eventually accepted.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Our plans to launch the new product hit a snag when we encountered a supply chain issue.</t>
+          <t>The company decided to take on five new interns for the summer.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ENG-20260527-322</t>
+          <t>ENG-20260527-422</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3296,44 +3296,44 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>drive a hard bargain</t>
+          <t>talk out of</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>/draɪv ə hɑrd ˈbɑrɡɪn/</t>
+          <t>/tɔːk aʊt ɒv/</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>흥정을 잘하다, 타협하지 않고 유리한 조건을 얻으려 하다</t>
+          <t>~에게 설득하여 ~을 하지 못하게 하다</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>European companies double down on China manufacturing despite EU de-risking push. (China often drives a hard bargain)</t>
+          <t>His friends tried to talk him out of quitting his stable job.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>He's known for being a tough negotiator; he always drives a hard bargain.</t>
+          <t>I managed to talk her out of buying that expensive dress she didn't need.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ENG-20260527-323</t>
+          <t>ENG-20260527-423</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3343,44 +3343,44 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>take the hit</t>
+          <t>tell apart</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>/teɪk ðə hɪt/</t>
+          <t>/tɛl əˈpɑːrt/</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>손해를 감수하다, 비난을 받다</t>
+          <t>~을 구별하다, 분간하다</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Energy bills to rise for millions as impact of Iran war hits. (Households will take the hit)</t>
+          <t>The twins look so similar; it's hard to tell them apart.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>The company decided to take the hit on profits rather than raise prices for loyal customers.</t>
+          <t>The two product models are so similar that only an expert can tell them apart.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ENG-20260527-324</t>
+          <t>ENG-20260527-424</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3390,44 +3390,44 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>call the shots</t>
+          <t>throw off</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>/kɔl ðə ʃɑts/</t>
+          <t>/θroʊ ɒf/</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>결정권을 쥐다, 지휘하다</t>
+          <t>혼란스럽게 하다, 방해하다; (냄새, 열 등을) 내뿜다</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>President Donald Trump last week endorsed Texas Attorney General Ken Paxton. (He calls the shots in his party)</t>
+          <t>The sudden change in the schedule threw off my entire day.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>As the project manager, she's the one who calls the shots.</t>
+          <t>The unexpected question completely threw him off during the interview.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ENG-20260527-325</t>
+          <t>ENG-20260527-425</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3437,44 +3437,44 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>clear the air</t>
+          <t>touch on</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>/klɪər ðɪ ɛər/</t>
+          <t>/tʌtʃ ɒn/</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>오해를 풀다, 관계를 명확히 하다</t>
+          <t>(주제 등을) 간단히 다루다, 언급하다</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Rachel: I swear you said you had the keys. Monica: But I didn't. (They need to clear the air after their argument)</t>
+          <t>The speaker briefly touched on the economic implications of the new policy.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>After their disagreement, they decided to meet for coffee to clear the air.</t>
+          <t>During the meeting, we only had time to touch on the main points.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ENG-20260527-326</t>
+          <t>ENG-20260527-426</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3489,39 +3489,39 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>give someone a heads-up</t>
+          <t>walk out on</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>/ɡɪv ˈsʌmˌwʌn ə ˈhɛdz ʌp/</t>
+          <t>/wɔːk aʊt ɒn/</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>~에게 미리 알려주다, 경고하다</t>
+          <t>~을 버리다, 갑자기 떠나다</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Chandler: The most unbelievable thing has happened. Underdog has just gotten away. (He gave them a heads-up about the balloon.)</t>
+          <t>He walked out on his family without saying a word, leaving them in financial difficulty.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Can you give me a heads-up if there are any changes to the schedule?</t>
+          <t>It was unprofessional for him to walk out on the project halfway through.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ENG-20260527-327</t>
+          <t>ENG-20260527-427</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3536,39 +3536,39 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>pull some strings</t>
+          <t>zone out</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>/pʊl sʌm strɪŋz/</t>
+          <t>/zoʊn aʊt/</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>배후에서 영향력을 행사하다, (인맥을 동원해) 일을 해결하다</t>
+          <t>멍하니 있다, 집중하지 못하다</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Joey: We have a copy of your key. (Joey might have to pull some strings to get the key faster.)</t>
+          <t>During the long lecture, I found myself zoning out and thinking about dinner.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>I had to pull some strings to get us tickets for the sold-out concert.</t>
+          <t>Sometimes I just zone out when I'm tired and need a break.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ENG-20260527-328</t>
+          <t>ENG-20260527-428</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>read the room</t>
+          <t>drum up business</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3593,29 +3593,29 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>/rid ðə rum/</t>
+          <t>/drʌm ʌp ˈbɪznɪs/</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>분위기를 파악하다, 상황을 읽다</t>
+          <t>손님을 모으다, 사업을 활성화하다</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Ross: I can't do this. Uh, this is too weird. I feel stupid. (He couldn't read the room well enough to just relax)</t>
+          <t>The new cafe is using social media to drum up business in the neighborhood.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>A good comedian knows how to read the room and adjust their jokes accordingly.</t>
+          <t>We need to come up with new strategies to drum up business during the off-peak season.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ENG-20260527-329</t>
+          <t>ENG-20260527-429</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>take something with a grain of salt</t>
+          <t>go the extra mile</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3640,29 +3640,29 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>/teɪk ˈsʌmθɪŋ wɪθ ə ɡreɪn ʌv sɔlt/</t>
+          <t>/ɡoʊ ðɪ ˈɛkstrə maɪl/</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>~을 액면 그대로 믿지 않다, 흘려듣다</t>
+          <t>특별히 더 노력하다, 최선을 다하다</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>SpaceX-Tesla merger chatter reignites as Musk pushes rocket company towards Nasdaq. (One should take merger rumors with a grain of salt.)</t>
+          <t>Our customer service team always goes the extra mile to ensure customer satisfaction.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>You should take his promises with a grain of salt; he often exaggerates.</t>
+          <t>To get that promotion, you'll really need to go the extra mile and impress your boss.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ENG-20260527-330</t>
+          <t>ENG-20260527-430</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>buy time</t>
+          <t>put out feelers</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3687,29 +3687,29 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>/baɪ taɪm/</t>
+          <t>/pʊt aʊt ˈfiːlərz/</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>시간을 벌다</t>
+          <t>탐색하다, 의향을 타진하다</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>The Post Office investigation could be delayed by five years. (This delay buys them time.)</t>
+          <t>Before launching the new product, we need to put out feelers to gauge market interest.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>We need to buy time to prepare a better proposal for the client.</t>
+          <t>I'm putting out feelers for a new job, quietly seeing what opportunities are available.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ENG-20260527-331</t>
+          <t>ENG-20260527-431</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>cut corners</t>
+          <t>keep an eye on</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3734,29 +3734,29 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>/kʌt ˈkɔrnərz/</t>
+          <t>/kiːp ən aɪ ɒn/</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>절차를 무시하고 대충 하다, 비용이나 노력을 절감하다</t>
+          <t>~을 주시하다, ~을 잘 살피다</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>European companies double down on China manufacturing despite EU de-risking push. (Some companies cut corners on safety)</t>
+          <t>Please keep an eye on the market trends while I'm away.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Don't cut corners on quality just to save a little money; it will cost more in the long run.</t>
+          <t>Can you keep an eye on my bag while I go to the restroom?</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ENG-20260527-332</t>
+          <t>ENG-20260527-432</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3766,12 +3766,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>face the music</t>
+          <t>make a point</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3781,29 +3781,29 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>/feɪs ðə ˈmjuːzɪk/</t>
+          <t>/meɪk ə pɔɪnt/</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>잘못에 대한 비난/벌을 받다, 결과를 감수하다</t>
+          <t>(특정 사실을) 강조하다, 역설하다</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>BP chairman removed due to 'bullying' behavior. He had to face the music.</t>
+          <t>She made a point of thanking every member of her team for their hard work.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>After neglecting his responsibilities, he finally had to face the music and deal with the consequences.</t>
+          <t>During the presentation, he made a point to highlight the company's achievements.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ENG-20260527-333</t>
+          <t>ENG-20260527-433</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3813,44 +3813,44 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>have second thoughts</t>
+          <t>turn a blind eye</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>/hæv ˈsɛkənd θɔts/</t>
+          <t>/tɜːrn ə blaɪnd aɪ/</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>다시 생각하다, 재고하다</t>
+          <t>못 본 척하다, 눈감아주다</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Ross: Ok, ok, ok, ok, here goes. You know, I, you know, can't do this. (He was having second thoughts about talking to the belly.)</t>
+          <t>The management was accused of turning a blind eye to the bullying behavior.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>I'm having second thoughts about accepting that job offer; it seems a bit risky.</t>
+          <t>You can't just turn a blind eye to the problems in our community.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ENG-20260527-334</t>
+          <t>ENG-20260527-434</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Modern Family</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>make ends meet</t>
+          <t>pull rank</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3875,29 +3875,29 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>/meɪk ɛndz mit/</t>
+          <t>/pʊl ræŋk/</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>수입과 지출의 균형을 맞추다, 겨우 생계를 유지하다</t>
+          <t>직위나 권한을 내세워 지시하다</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Americans are 'entrenched' in financial stress amid debt and price pressures. (Many struggle to make ends meet.)</t>
+          <t>Instead of debating, the manager just pulled rank and made a unilateral decision.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>It's becoming increasingly difficult for families to make ends meet with the rising cost of living.</t>
+          <t>Don't try to pull rank on me; we're all equals in this project.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ENG-20260527-335</t>
+          <t>ENG-20260527-435</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>play it by ear</t>
+          <t>pay lip service</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3922,29 +3922,29 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>/pleɪ ɪt baɪ iər/</t>
+          <t>/peɪ lɪp ˈsɜːrvɪs/</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>상황 봐서 즉흥적으로 처리하다</t>
+          <t>겉으로만 동의하거나 지지하는 척하다, 입발림을 하다</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Rachel: We're waiting for you to open the door. You got the keys. (They might have to play it by ear to get inside.)</t>
+          <t>Critics argue that the company only pays lip service to environmental protection without real action.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>We don't have a strict plan for the weekend; let's just play it by ear.</t>
+          <t>Many politicians pay lip service to helping the poor but do little in practice.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ENG-20260527-336</t>
+          <t>ENG-20260527-436</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3954,44 +3954,44 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>sleep on it</t>
+          <t>give someone the green light</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>/slip ɑn ɪt/</t>
+          <t>/ɡɪv ˌsʌmwʌn ðə ɡriːn laɪt/</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>하룻밤 자면서 곰곰이 생각하다 (결정을 미루다)</t>
+          <t>~에게 허락하다, 승인하다</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Carol: So don't do it, it's fine. You don't have to do it just because Susan does it. (Ross could sleep on it before deciding to sing)</t>
+          <t>The board finally gave the team the green light to proceed with the experimental project.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>That's a big decision, so why don't you sleep on it and tell me your answer tomorrow?</t>
+          <t>Once we get the green light from legal, we can start advertising the new service.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ENG-20260527-337</t>
+          <t>ENG-20260527-437</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>take a rain check</t>
+          <t>give someone the benefit of the doubt</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4016,29 +4016,29 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>/teɪk ə reɪn tʃɛk/</t>
+          <t>/ɡɪv ˌsʌmwʌn ðə ˈbɛnɪfɪt ɒv ðə daʊt/</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>다음 기회로 미루다, (초대를) 나중에 받아들이다</t>
+          <t>일단 믿어주다, 좋게 봐주다</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Rachel: I can't, I gotta go. (She had to take a rain check on going to the roof.)</t>
+          <t>Despite the mixed reviews, I decided to give the new restaurant the benefit of the doubt.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>I'm too busy to go out tonight, but can I take a rain check?</t>
+          <t>He's usually very reliable, so I'll give him the benefit of the doubt about being late today.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ENG-20260527-338</t>
+          <t>ENG-20260527-438</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4048,12 +4048,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>miss the boat</t>
+          <t>break the bank</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4063,29 +4063,29 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>/mɪs ðə boʊt/</t>
+          <t>/breɪk ðə bæŋk/</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>기회를 놓치다</t>
+          <t>엄청난 돈을 쓰다, 거액을 지출하다</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>SK Hynix hits $1 trillion valuation as AI boom lifts South Korean chip stocks. (Investors who didn't buy early missed the boat.)</t>
+          <t>Getting better WiFi for hundreds of trains shouldn't break the bank for the government.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>If you don't apply for the scholarship soon, you'll miss the boat.</t>
+          <t>We want a nice vacation, but we don't want to break the bank.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ENG-20260527-339</t>
+          <t>ENG-20260527-439</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4100,39 +4100,39 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>pick someone's brain</t>
+          <t>foot the bill</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>/pɪk ˈsʌmˌwʌnz breɪn/</t>
+          <t>/fʊt ðə bɪl/</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>~에게 조언을 구하다, 지식을 얻다</t>
+          <t>계산하다, 비용을 부담하다</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Chompie, one of the world's tops ethical hackers, says AI like Claude Mythos will make it harder for people like her to compete. (Perhaps others want to pick Chompie's brain.)</t>
+          <t>The government will foot the bill for the WiFi upgrade on the trains.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>I'd love to pick your brain sometime about your experience in the tech industry.</t>
+          <t>My company offered to foot the bill for my further education.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ENG-20260527-340</t>
+          <t>ENG-20260527-440</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>tighten the belt</t>
+          <t>piece of cake</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4157,29 +4157,29 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>/ˈtaɪtən ðə bɛlt/</t>
+          <t>/piːs ɒv keɪk/</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>허리띠를 졸라매다, 지출을 줄이다</t>
+          <t>매우 쉬운 일</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Americans are 'entrenched' in financial stress amid debt and price pressures. (Many have to tighten their belts.)</t>
+          <t>Don't worry about the exam; it'll be a piece of cake if you've studied.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>With rising inflation, many families are having to tighten their belts and cut back on non-essential spending.</t>
+          <t>Learning to use the new software was a piece of cake for him.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ENG-20260527-341</t>
+          <t>ENG-20260527-441</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>call it a day</t>
+          <t>back to the drawing board</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4204,29 +4204,29 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>/kɔl ɪt ə deɪ/</t>
+          <t>/bæk tuː ðə ˈdrɔːɪŋ bɔːrd/</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>하루 일을 마치다, 끝내다</t>
+          <t>원점으로 돌아가 다시 시작하다</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Ok, all done. (Phoebe was ready to call it a day on the potatoes)</t>
+          <t>Our first attempt failed, so it's back to the drawing board for the entire team.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>It's getting late; let's call it a day and pick this up tomorrow morning.</t>
+          <t>The client rejected our proposal, so we're back to the drawing board to come up with new ideas.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ENG-20260527-342</t>
+          <t>ENG-20260527-442</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>spill the beans</t>
+          <t>jump on the bandwagon</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4251,29 +4251,29 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>/spɪl ðə binz/</t>
+          <t>/dʒʌmp ɒn ðə ˈbændˌwæɡən/</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>비밀을 누설하다, 다 불어버리다</t>
+          <t>시류에 편승하다, 유행을 따르다</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Chandler: The most unbelievable thing has happened. Underdog has just gotten away. (He's spilling the beans about the event.)</t>
+          <t>Many investors are jumping on the AI bandwagon hoping for quick profits.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Don't spill the beans about the surprise party; it's a secret!</t>
+          <t>After seeing the success of their competitor, they decided to jump on the bandwagon and offer similar services.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ENG-20260527-343</t>
+          <t>ENG-20260527-443</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>hit the ground running</t>
+          <t>get a handle on</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4298,29 +4298,29 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>/hɪt ðə ɡraʊnd ˈrʌnɪŋ/</t>
+          <t>/ɡɛt ə ˈhændl ɒn/</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>즉시 활발하게 일을 시작하다, 빠른 속도로 진행하다</t>
+          <t>~을 이해하고 통제하다, 다루는 방법을 알다</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Booming AI chip demand helps create two new $1tn club members. (New companies hit the ground running.)</t>
+          <t>It took me a while to get a handle on the new software's features.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Our new marketing intern hit the ground running and quickly became an invaluable part of the team.</t>
+          <t>We need to get a handle on our expenses before they get out of control.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ENG-20260527-344</t>
+          <t>ENG-20260527-444</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>go with the flow</t>
+          <t>have a lot on one's plate</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4345,29 +4345,29 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>/ɡoʊ wɪθ ðə floʊ/</t>
+          <t>/hæv ə lɒt ɒn wʌnz pleɪt/</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>흐름에 따르다, 순리에 맡기다</t>
+          <t>할 일이 많다, 책임이 많다</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Phoebe: Oh, I'm sorry, oh, I just, I thought we could have them whipped. (Monica doesn't go with the flow easily.)</t>
+          <t>With the upcoming merger and new product launch, the CEO has a lot on her plate.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>My travel plans are flexible; I'll just go with the flow and see where the journey takes me.</t>
+          <t>I can't take on any more tasks right now; I already have a lot on my plate.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ENG-20260527-345</t>
+          <t>ENG-20260527-445</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>bite the bullet</t>
+          <t>keep one's head above water</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4392,29 +4392,29 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>/baɪt ðə ˈbʊlɪt/</t>
+          <t>/kiːp wʌnz hɛd əˈbʌv ˈwɔːtər/</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>어려움을 감수하다, 이를 악물고 참다</t>
+          <t>빚지지 않고 겨우 살아가다, 재정적 어려움 속에서 버티다</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Energy bills to rise for millions as impact of Iran war hits. (People will have to bite the bullet.)</t>
+          <t>Many small businesses are struggling to keep their heads above water during the economic downturn.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>I really don't want to work extra hours, but I'll have to bite the bullet to finish this project on time.</t>
+          <t>With rising inflation, it's hard for single parents to keep their heads above water.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ENG-20260527-346</t>
+          <t>ENG-20260527-446</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>break a leg</t>
+          <t>up in the air</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4439,29 +4439,29 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>/breɪk ə lɛɡ/</t>
+          <t>/ʌp ɪn ðɪ ɛər/</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>행운을 빌다 (특히 공연 전에)</t>
+          <t>미정인, 불확실한</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Ross: Ok, ok, here we go. (Someone might wish him 'break a leg' before his 'performance' for the baby.)</t>
+          <t>Our travel plans for the summer are still up in the air due to the uncertain situation.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>You have your big presentation today? Break a leg!</t>
+          <t>The future of the project is still up in the air, awaiting board approval.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ENG-20260527-347</t>
+          <t>ENG-20260527-447</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4471,12 +4471,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Modern Family</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>cost an arm and a leg</t>
+          <t>a drop in the bucket</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4486,29 +4486,29 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>/kɔst æn ɑrm ənd ə lɛɡ/</t>
+          <t>/ə drɒp ɪn ðə ˈbʌkɪt/</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>매우 비싸다, 엄청난 비용이 들다</t>
+          <t>새 발의 피, 극히 일부에 지나지 않는 양</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Ferrari shares slump after it unveils first fully electric car. (The new car likely costs an arm and a leg.)</t>
+          <t>The initial investment was just a drop in the bucket compared to the total cost of the project.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>I'd love to buy a house in this neighborhood, but it would cost an arm and a leg.</t>
+          <t>Our contribution to the charity felt like a drop in the bucket, but every bit helps.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ENG-20260527-348</t>
+          <t>ENG-20260527-448</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>get something off one's chest</t>
+          <t>actions speak louder than words</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4533,29 +4533,29 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>/ɡɛt ˈsʌmθɪŋ ɔf wʌnz tʃɛst/</t>
+          <t>/ˈækʃənz spiːk ˈlaʊdər ðæn wɜːrdz/</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>마음속의 고민을 털어놓다</t>
+          <t>말보다 행동이 더 중요하다</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Ross: I can't do this. Uh, this is too weird. I feel stupid. (He wants to get this off his chest.)</t>
+          <t>He keeps promising to change, but actions speak louder than words.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>I've been worried about this for days; I need to get it off my chest.</t>
+          <t>Instead of just talking about sustainability, the company showed that actions speak louder than words with its new eco-friendly products.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ENG-20260527-349</t>
+          <t>ENG-20260527-449</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>Modern Family</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>let the cat out of the bag</t>
+          <t>add fuel to the fire</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4580,29 +4580,29 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>/lɛt ðə kæt aʊt ʌv ðə bæɡ/</t>
+          <t>/æd fjuːəl tuː ðə ˈfaɪər/</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>비밀을 누설하다, 폭로하다</t>
+          <t>불난 집에 부채질하다, 상황을 악화시키다</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Chandler: The most unbelievable thing has happened. Underdog has just gotten away. (He let the cat out of the bag about the balloon incident.)</t>
+          <t>His sarcastic remark only added fuel to the fire during the heated discussion.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>We were planning a surprise party for her, but my brother accidentally let the cat out of the bag.</t>
+          <t>Don't mention the layoffs, you'll just add fuel to the fire of employee discontent.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ENG-20260527-350</t>
+          <t>ENG-20260527-450</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4612,12 +4612,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>lose one's touch</t>
+          <t>all in the same boat</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4627,29 +4627,29 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>/luːz wʌnz tʌtʃ/</t>
+          <t>/ɔːl ɪn ðə seɪm boʊt/</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>감각을 잃다, 실력이 떨어지다</t>
+          <t>모두 같은 처지에 있다, 한 배를 타다</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Joey: Hey, I got one keyhole and about a zillion keys. (He might feel like he's losing his touch at picking locks.)</t>
+          <t>With rising inflation, we're all in the same boat, trying to cut down on expenses.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>The chef felt he was losing his touch when his famous dish didn't turn out well.</t>
+          <t>During the pandemic, remote workers and office workers were all in the same boat, adapting to new routines.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ENG-20260527-351</t>
+          <t>ENG-20260527-451</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>stab someone in the back</t>
+          <t>barking up the wrong tree</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4674,29 +4674,29 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>/stæb ˈsʌmˌwʌn ɪn ðə bæk/</t>
+          <t>/ˈbɑːrkɪŋ ʌp ðə rɒŋ triː/</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>~를 배신하다, 뒤통수치다</t>
+          <t>엉뚱한 사람을 비난하거나 엉뚱한 방향으로 추측하다</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Paxton bests Cornyn in Texas Republican Senate primary after Trump endorsement. (Some might see the endorsement as a stab in the back for Cornyn.)</t>
+          <t>If you think I'm responsible for this mistake, you're barking up the wrong tree.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>I can't believe he stabbed me in the back by telling my secret to everyone.</t>
+          <t>The police were barking up the wrong tree until they found new evidence.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ENG-20260527-352</t>
+          <t>ENG-20260527-452</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>the ball is in one's court</t>
+          <t>by the book</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4721,29 +4721,29 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>/ðə bɔl ɪz ɪn wʌnz kɔrt/</t>
+          <t>/baɪ ðə bʊk/</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>(결정이나 행동의) 책임이 ~에게 있다</t>
+          <t>규칙대로, 원칙대로</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Monica: No I don't. Rachel: Yes, you do. When we left, you said, 'got the keys.' (The ball was in Monica's court to find the keys.)</t>
+          <t>The auditors always do everything by the book, leaving no room for error.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>I've made my offer, so now the ball is in your court to accept or decline.</t>
+          <t>We have to handle this situation strictly by the book to avoid any legal issues.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ENG-20260527-353</t>
+          <t>ENG-20260527-453</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Modern Family</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>throw in the towel</t>
+          <t>come hell or high water</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4768,29 +4768,29 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>/θroʊ ɪn ðə ˈtaʊəl/</t>
+          <t>/kʌm hɛl ɔːr haɪ ˈwɔːtər/</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>포기하다, 항복하다</t>
+          <t>어떤 어려움이 있어도, 무슨 수를 써서라도</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Farmers' warning as milk prices fall below cost. (Some farmers might be forced to throw in the towel.)</t>
+          <t>Come hell or high water, we will finish this project on time.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>After several failed attempts, he was ready to throw in the towel, but his coach encouraged him to keep going.</t>
+          <t>He promised to be there for her, come hell or high water.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ENG-20260527-354</t>
+          <t>ENG-20260527-454</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>under the weather</t>
+          <t>cross that bridge when we come to it</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4815,29 +4815,29 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>/ˈʌndər ðə ˈwɛðər/</t>
+          <t>/krɒs ðæt brɪdʒ wɛn wiː kʌm tuː ɪt/</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>몸이 안 좋다, 약간 아프다</t>
+          <t>닥쳐서 해결하다, 미리 걱정하지 않다</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Ross: I feel stupid. (He might also feel a bit under the weather from the stress.)</t>
+          <t>I know there might be a problem with funding, but we'll cross that bridge when we come to it.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>I'm feeling a bit under the weather today, so I might go home early.</t>
+          <t>We don't know yet if we'll need extra staff; we'll cross that bridge when we come to it.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ENG-20260527-355</t>
+          <t>ENG-20260527-455</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>back to square one</t>
+          <t>cut to the chase</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4862,29 +4862,29 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>/bæk tuː skwɛər wʌn/</t>
+          <t>/kʌt tuː ðə tʃeɪs/</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>원점으로 돌아가다, 처음부터 다시 시작하다</t>
+          <t>바로 본론으로 들어가다</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Joey: Nope, not that one. (If none of the keys work, they're back to square one.)</t>
+          <t>Let's cut to the chase and discuss the main issue without further delay.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Our entire experiment failed, so we're back to square one with our research.</t>
+          <t>I don't have much time, so please just cut to the chase.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ENG-20260527-356</t>
+          <t>ENG-20260527-456</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>beat around the bush</t>
+          <t>don't put all your eggs in one basket</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4909,29 +4909,29 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>/bit əˈraʊnd ðə bʊʃ/</t>
+          <t>/doʊnt pʊt ɔːl jʊər ɛɡz ɪn wʌn ˈbɑːskɪt/</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>빙빙 돌려 말하다, 요점을 피하다</t>
+          <t>모든 것을 한 곳에 집중하지 마라, 분산 투자해라</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Ross: Ok, where am I talking to, here? I mean, uh, well, there is one way that seems to offer a certain acoustical advantage, but... (Ross is beating around the bush.)</t>
+          <t>It's wise not to put all your eggs in one basket, especially when investing in volatile stocks.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Stop beating around the bush and just tell me what you want to say.</t>
+          <t>When looking for a job, don't put all your eggs in one basket; apply to multiple companies.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ENG-20260527-357</t>
+          <t>ENG-20260527-457</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4941,12 +4941,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>bless someone's heart</t>
+          <t>easier said than done</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4956,29 +4956,29 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>/blɛs ˈsʌmˌwʌnz hɑrt/</t>
+          <t>/ˈiːziər sɛd ðæn dʌn/</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>(남을 동정하거나 살짝 비꼬는 의미로) 안쓰럽네, 착한 심성 가진 사람</t>
+          <t>말이야 쉽지, 실행은 어렵다</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Phoebe: Yeah, but did they have to shoot him down? I mean, that was just mean. (She might say 'bless their hearts' to the people who shot down the balloon.)</t>
+          <t>Saving money during high inflation is easier said than done for many families.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Bless her heart, she tried her best, even though she clearly had no idea what she was doing.</t>
+          <t>Quitting smoking is easier said than done for many people.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ENG-20260527-358</t>
+          <t>ENG-20260527-458</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>burn the midnight oil</t>
+          <t>every cloud has a silver lining</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5003,29 +5003,29 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>/bɜrn ðə ˈmɪdˌnaɪt ɔɪl/</t>
+          <t>/ˈɛvri klaʊd hæz ə ˈsɪlvər ˈlaɪnɪŋ/</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>밤늦게까지 일하다, 밤샘하다</t>
+          <t>모든 불행에는 한 줄기 희망이 있다, 전화위복</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>The Post Office investigation team would need to double in order to meet its current timeline. (They might have to burn the midnight oil.)</t>
+          <t>Losing that job was tough, but I found a better one. Every cloud has a silver lining.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>I had to burn the midnight oil to finish my report before the deadline.</t>
+          <t>Even during difficult times, remember that every cloud has a silver lining.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ENG-20260527-359</t>
+          <t>ENG-20260527-459</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>can't make heads or tails of</t>
+          <t>get a taste of one's own medicine</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5050,29 +5050,29 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>/kænt meɪk hɛdz ɔr teɪlz ʌv/</t>
+          <t>/ɡɛt ə teɪst ɒv wʌnz oʊn ˈmɛdɪsɪn/</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>~을 도무지 이해할 수 없다</t>
+          <t>자신이 남에게 행했던 나쁜 일을 그대로 당하다, 자업자득</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Ross: And you have no idea what I'm saying, because, let's face it, you're a fetus. (The fetus can't make heads or tails of what Ross is saying.)</t>
+          <t>After constantly criticizing his colleagues, he finally got a taste of his own medicine when his project failed.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>I've read these instructions three times, but I still can't make heads or tails of them.</t>
+          <t>She was always spreading rumors, and now she's getting a taste of her own medicine.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ENG-20260527-360</t>
+          <t>ENG-20260527-460</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5087,39 +5087,39 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>chew someone out</t>
+          <t>get out of hand</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>/tʃuː ˈsʌmˌwʌn aʊt/</t>
+          <t>/ɡɛt aʊt ɒv hænd/</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>~를 호되게 꾸짖다, 야단치다</t>
+          <t>통제 불능이 되다, 걷잡을 수 없게 되다</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Monica: (angry) Joey! (She's about to chew him out for being slow with the keys.)</t>
+          <t>The party started to get out of hand, so we decided to leave early.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>My boss chewed me out for being late to the important meeting.</t>
+          <t>If we don't address these small issues now, they might get out of hand later.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ENG-20260527-361</t>
+          <t>ENG-20260527-461</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>come clean</t>
+          <t>get the ball rolling</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5144,22 +5144,22 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>/kʌm klin/</t>
+          <t>/ɡɛt ðə bɔːl ˈroʊlɪŋ/</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>솔직하게 털어놓다, 고백하다</t>
+          <t>일을 시작하다, 추진하다</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Rachel: I swear you said you had the keys. Monica: But I didn't. (One of them needs to come clean about the keys.)</t>
+          <t>Let's get the ball rolling on this new marketing campaign right away.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>After weeks of hiding it, he finally decided to come clean about breaking the vase.</t>
+          <t>We need to get the ball rolling on our preparations for the annual conference.</t>
         </is>
       </c>
     </row>

--- a/data/02_Daily_Sheets/Expressions_2026-05-27.xlsx
+++ b/data/02_Daily_Sheets/Expressions_2026-05-27.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ENG-20260527-362</t>
+          <t>ENG-20260527-462</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -476,44 +476,44 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>push back against</t>
+          <t>trim losses</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>/pʊʃ bæk əˈɡɛnst/</t>
+          <t>/trɪm ˈlɒsɪz/</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>반대하거나 저항하다, 반발하다</t>
+          <t>손실을 줄이다, 손실 폭을 좁히다</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Former BP Chairman Albert Manifold has pushed back against accusations over his conduct following his shock departure.</t>
+          <t>U.S. crude oil prices trim losses as traders assess whether U.S. is nearing a deal with Iran.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The employees decided to push back against the new policy regarding remote work.</t>
+          <t>The company implemented aggressive cost-cutting measures to trim losses in the last quarter.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ENG-20260527-363</t>
+          <t>ENG-20260527-463</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -528,39 +528,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ink a deal</t>
+          <t>stare down</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>/ɪŋk ə diːl/</t>
+          <t>/stɛər daʊn/</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>계약에 서명하다, 거래를 성사시키다</t>
+          <t>(어려움, 위협 등에) 맞서다, 정면으로 응시하다, 위협에 굴하지 않다</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Everyone is speculating if SpaceX and Tesla will ink a deal for a potential tie-up soon.</t>
+          <t>Republicans stare down inflation abyss with midterms fast approaching.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>The startup is close to inking a deal with a major investor.</t>
+          <t>The new CEO had to stare down a potential employee strike in her first month.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ENG-20260527-364</t>
+          <t>ENG-20260527-464</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -575,39 +575,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>come out in force</t>
+          <t>push for</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>/kʌm aʊt ɪn fɔːrs/</t>
+          <t>/pʊʃ fɔːr/</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>많은 수가 집결하다, 대거 나타나다</t>
+          <t>~을 강력히 요구하다, ~을 추진하다</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>After the Trump endorsement, voters were expected to come out in force for Paxton.</t>
+          <t>President Trump pushes for funding for a White House ballroom, while Republicans struggle to find a clear message.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Despite the bad weather, fans came out in force to support their favorite team.</t>
+          <t>Environmental groups continue to push for stricter regulations on carbon emissions.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ENG-20260527-365</t>
+          <t>ENG-20260527-465</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>throw one's weight behind</t>
+          <t>be on the lookout</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -632,29 +632,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>/θroʊ wʌnz weɪt bɪˈhaɪnd/</t>
+          <t>/bi ɒn ðə ˈlʊkˌaʊt/</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>누군가나 무언가를 적극적으로 지지하고 영향력을 행사하다</t>
+          <t>~을 경계하다, ~을 찾다, ~에 대해 주의를 기울이다</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>President Trump threw his weight behind Texas Attorney General Ken Paxton, impacting the primary results.</t>
+          <t>Jamie Dimon says JPMorgan Chase could spend $20 billion on acquisition: 'We are on the lookout.'</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>The CEO decided to throw her weight behind the new sustainability initiative.</t>
+          <t>We need to be on the lookout for new talent to join our expanding team.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ENG-20260527-366</t>
+          <t>ENG-20260527-466</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -664,44 +664,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>beef up</t>
+          <t>invite scrutiny</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>/biːf ʌp/</t>
+          <t>/ɪnˈvaɪt ˈskruːtəni/</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강화하다, 보강하다</t>
+          <t>정밀 조사/감독을 초래하다, 의혹을 사다</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Russia needs to beef up its anti-drone defense systems to counter attacks.</t>
+          <t>A $20 billion deal could invite regulatory scrutiny given its position as the largest U.S. bank.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>The company plans to beef up its cybersecurity measures after a recent data breach.</t>
+          <t>Their recent accounting practices are likely to invite scrutiny from the IRS.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ENG-20260527-367</t>
+          <t>ENG-20260527-467</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -711,44 +711,44 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>take a nosedive</t>
+          <t>pull back</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>/teɪk ə ˈnoʊzdaɪv/</t>
+          <t>/pʊl bæk/</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>급락하다, 폭락하다</t>
+          <t>물러나다, 손을 떼다, (투자 등을) 회수하다</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Ferrari shares took a nosedive after it unveiled its first fully electric car to a divided public.</t>
+          <t>Homebuyers also pulled back but were still more active than last year.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>After the scandal, the politician's approval ratings took a nosedive.</t>
+          <t>Investors began to pull back from the volatile stock market after the news.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ENG-20260527-368</t>
+          <t>ENG-20260527-468</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -763,39 +763,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>hit a record high</t>
+          <t>ramp up</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>/hɪt ə ˈrɛkərd haɪ/</t>
+          <t>/ræmp ʌp/</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>최고 기록을 경신하다</t>
+          <t>~을 늘리다, 강화하다, 증대시키다</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SK Hynix shares hit a record high, pushing its valuation above $1 trillion.</t>
+          <t>Boeing CEO says company met requirements to increase 737 Max production to 47 jets per month, essentially to ramp up its production.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Oil prices hit a record high last month, causing concerns for consumers.</t>
+          <t>We need to ramp up our marketing efforts before the product launch next month.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ENG-20260527-369</t>
+          <t>ENG-20260527-469</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -810,39 +810,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>take off</t>
+          <t>meet requirements</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>/teɪk ɒf/</t>
+          <t>/miːt rɪˈkwaɪərmənts/</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>갑자기 성공하다, 인기를 얻다; (주식 등이) 급등하다</t>
+          <t>요구 사항을 충족시키다</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>The AI rally resumed, and many tech stocks started to take off again.</t>
+          <t>Boeing CEO says company met requirements to increase 737 Max production.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Her new business really started to take off after a successful marketing campaign.</t>
+          <t>The new software successfully meets all the client's security requirements.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ENG-20260527-370</t>
+          <t>ENG-20260527-470</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -852,44 +852,44 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>feel the pinch</t>
+          <t>appeal to</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>/fiːl ðə pɪntʃ/</t>
+          <t>/əˈpiːl tuː/</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>재정적 어려움을 느끼다, 궁핍함을 겪다</t>
+          <t>~의 흥미/관심을 끌다, ~에게 매력적으로 보이다</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Americans are feeling the pinch as inflation and high debt levels continue to cause financial anxiety.</t>
+          <t>The advertising watchdog said the adverts featuring top footballers had a strong appeal to under-18s.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Many families are starting to feel the pinch with the rising cost of living.</t>
+          <t>The vibrant packaging is designed to appeal to younger consumers.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ENG-20260527-371</t>
+          <t>ENG-20260527-471</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -899,44 +899,44 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>tighten one's belt</t>
+          <t>follow up on</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>/ˈtaɪtn wʌnz bɛlt/</t>
+          <t>/ˈfɒloʊ ʌp ɒn/</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>허리띠를 졸라매다, 지출을 줄이다</t>
+          <t>~에 대해 후속 조치를 취하다, 추가 확인하다</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>With energy bills set to rise, many households will have to tighten their belts.</t>
+          <t>I need to follow up on that email I sent to the client last week.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Due to the economic downturn, we'll all have to tighten our belts for a while.</t>
+          <t>Please follow up on the status of those overdue invoices.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ENG-20260527-372</t>
+          <t>ENG-20260527-472</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>drag on</t>
+          <t>fall through</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -961,29 +961,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>/dræɡ ɒn/</t>
+          <t>/fɔːl θruː/</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>지루하게 오래 계속되다, 지연되다</t>
+          <t>(계획, 협상 등이) 수포로 돌아가다, 실패하다</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>The Post Office investigation could drag on for another five years if resources aren't increased.</t>
+          <t>Our plans for the weekend fell through because of the sudden change in weather.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>The negotiations have been dragging on for weeks without a clear resolution.</t>
+          <t>The acquisition deal almost fell through due to disagreements over intellectual property rights.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ENG-20260527-373</t>
+          <t>ENG-20260527-473</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -993,44 +993,44 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>put on hold</t>
+          <t>bail out</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>/pʊt ɒn hoʊld/</t>
+          <t>/beɪl aʊt/</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>보류하다, 연기하다</t>
+          <t>(어려움에 처한 사람/회사 등을) 돕다, 구제하다</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>The Post Office investigation might be put on hold due to a lack of resources.</t>
+          <t>The government had to bail out several banks during the financial crisis.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>We've decided to put the new project on hold until next quarter.</t>
+          <t>We had to bail out our friend who got into trouble overseas.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ENG-20260527-374</t>
+          <t>ENG-20260527-474</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1040,44 +1040,44 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>stay ahead of the curve</t>
+          <t>chew out</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>/steɪ əˈhɛd ɒv ðə kɜːrv/</t>
+          <t>/tʃuː aʊt/</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>트렌드나 경쟁에서 앞서나가다, 시대를 앞서가다</t>
+          <t>~을 꾸짖다, 심하게 야단치다</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Chompie warns that ethical hackers need to stay ahead of the curve as AI tools evolve.</t>
+          <t>My boss really chewed me out for missing the deadline.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>To remain competitive, companies must constantly innovate and stay ahead of the curve.</t>
+          <t>The coach chewed out the players for their poor performance in the first half.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ENG-20260527-375</t>
+          <t>ENG-20260527-475</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1087,44 +1087,44 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>up one's game</t>
+          <t>call for</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>/ʌp wʌnz ɡeɪm/</t>
+          <t>/kɔːl fɔːr/</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>실력을 향상시키다, 더 잘하다</t>
+          <t>~을 요구하다, ~을 필요로 하다</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>The rise of AI tools means human hackers will have to up their game to compete.</t>
+          <t>The environmental report calls for immediate action to reduce pollution levels.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>If you want that promotion, you'll really need to up your game in sales.</t>
+          <t>This situation calls for a calm and rational approach.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ENG-20260527-376</t>
+          <t>ENG-20260527-476</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>crack down on</t>
+          <t>square away</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1149,29 +1149,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>/kræk daʊn ɒn/</t>
+          <t>/skwɛər əˈweɪ/</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>단속하다, 엄격하게 규제하다</t>
+          <t>(일 등을) 정리하다, 마무리하다</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>The advertising watchdog decided to crack down on Instagram betting ads featuring footballers.</t>
+          <t>I need to square away a few things before I can leave for vacation.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>The government is cracking down on tax evasion to boost revenue.</t>
+          <t>Let's square away the paperwork so we can proceed with the project.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ENG-20260527-377</t>
+          <t>ENG-20260527-477</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>iron out</t>
+          <t>come up with</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1196,29 +1196,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>/ˈaɪərn aʊt/</t>
+          <t>/kʌm ʌp wɪð/</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>(문제, 오해 등을) 해결하다, 해소하다</t>
+          <t>~을 생각해내다, 제안하다</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Before the merger can proceed, both companies need to iron out a few legal details.</t>
+          <t>They had to come up with a new strategy after their initial plan failed.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Let's meet tomorrow to iron out the final details of the proposal.</t>
+          <t>Can you come up with some innovative ideas for our next product launch?</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ENG-20260527-378</t>
+          <t>ENG-20260527-478</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>hammer out</t>
+          <t>come down with</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1243,29 +1243,29 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>/ˈhæmər aʊt/</t>
+          <t>/kʌm daʊn wɪð/</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>협의나 논의를 거쳐 (합의, 계획 등을) 힘들게 도출해내다</t>
+          <t>(질병에) 걸리다</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>The two sides spent all night trying to hammer out a compromise on the budget.</t>
+          <t>I think I'm coming down with a cold, I feel a bit under the weather.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>They finally hammered out a new contract after weeks of negotiation.</t>
+          <t>She couldn't attend the meeting because she came down with the flu.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ENG-20260527-379</t>
+          <t>ENG-20260527-479</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>call out</t>
+          <t>get across</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1290,29 +1290,29 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>/kɔːl aʊt/</t>
+          <t>/ɡɛt əˈkrɒs/</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>비판하다, 잘못을 지적하다; (도움을 요청하며) 부르다</t>
+          <t>(의미, 메시지 등을) 전달하다, 이해시키다</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>The employee decided to call out the bullying behavior of their superior.</t>
+          <t>It was difficult to get my point across during the heated discussion.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>It's important to call out discriminatory remarks when you hear them.</t>
+          <t>The speaker struggled to get her complex ideas across to the general audience.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ENG-20260527-380</t>
+          <t>ENG-20260527-480</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>opt out of</t>
+          <t>get around to</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1337,29 +1337,29 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>/ɒpt aʊt ɒv/</t>
+          <t>/ɡɛt əˈraʊnd tuː/</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>선택하지 않다, ~에서 빠져나가다</t>
+          <t>(미뤄왔던 일을) 마침내 하다</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Many students are choosing to opt out of the traditional university system for vocational training.</t>
+          <t>I still haven't gotten around to organizing my files, but I will soon.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Employees can opt out of the company's health insurance plan if they have their own.</t>
+          <t>I hope to get around to calling my parents this weekend.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ENG-20260527-381</t>
+          <t>ENG-20260527-481</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>phase out</t>
+          <t>zoom in on</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1384,29 +1384,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>/feɪz aʊt/</t>
+          <t>/zuːm ɪn ɒn/</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>단계적으로 중단하다, 폐지하다</t>
+          <t>~에 초점을 맞추다, 집중하다</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>The company plans to phase out its old product line to make way for new innovations.</t>
+          <t>The analyst decided to zoom in on the specific details of the company's financial report.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>The government is trying to phase out the use of plastic bags over the next few years.</t>
+          <t>The team needs to zoom in on the most critical customer feedback to improve the product.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ENG-20260527-382</t>
+          <t>ENG-20260527-482</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>reel in</t>
+          <t>go through with</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1431,29 +1431,29 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>/riːl ɪn/</t>
+          <t>/ɡoʊ θruː wɪð/</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>유인하여 끌어들이다 (특히 고객, 투자자 등)</t>
+          <t>(계획, 약속 등을) 실행하다, 끝까지 해내다</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>The new marketing campaign aims to reel in more subscribers to our streaming service.</t>
+          <t>Despite his doubts, he decided to go through with the difficult surgery.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>They used celebrity endorsements to reel in a younger demographic.</t>
+          <t>Are you really going to go through with selling your house in this market?</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ENG-20260527-383</t>
+          <t>ENG-20260527-483</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>weigh in</t>
+          <t>weigh in on</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1478,29 +1478,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>/weɪ ɪn/</t>
+          <t>/weɪ ɪn ɒn/</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>논쟁이나 토론에 의견을 보태다, 개입하다</t>
+          <t>~에 대해 의견을 제시하다, 한마디 거들다</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Several industry experts weighed in on the potential SpaceX-Tesla merger chatter.</t>
+          <t>Everyone wanted to weigh in on the controversial decision during the meeting.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>The CEO decided to weigh in on the controversial decision during the board meeting.</t>
+          <t>The expert was asked to weigh in on the potential impact of the new regulations.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ENG-20260527-384</t>
+          <t>ENG-20260527-484</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>hold off on</t>
+          <t>fill in for</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1525,29 +1525,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>/hoʊld ɒf ɒn/</t>
+          <t>/fɪl ɪn fɔːr/</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>~을 보류하다, ~을 미루다</t>
+          <t>~을 대신하다, 대리하다</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Let's hold off on making a final decision until we have all the information.</t>
+          <t>Could you fill in for me at the meeting tomorrow? I'm feeling unwell.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>They decided to hold off on their travel plans until the pandemic situation improves.</t>
+          <t>The junior analyst had to fill in for her manager who was on paternity leave.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ENG-20260527-385</t>
+          <t>ENG-20260527-485</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>step down</t>
+          <t>push back</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1572,29 +1572,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>/stɛp daʊn/</t>
+          <t>/pʊʃ bæk/</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>사임하다, 물러나다</t>
+          <t>(일정, 마감일 등을) 미루다, 연기하다</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>The chairman was forced to step down after accusations of misconduct.</t>
+          <t>We had to push back the project deadline by a week due to unforeseen delays.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>She announced her decision to step down as CEO at the end of the year.</t>
+          <t>Can we push back our meeting to Friday afternoon instead of Thursday morning?</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ENG-20260527-386</t>
+          <t>ENG-20260527-486</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1609,39 +1609,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>step up</t>
+          <t>get something off the ground</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>/stɛp ʌp/</t>
+          <t>/ɡɛt ˈsʌmθɪŋ ɒf ðə ɡraʊnd/</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>더 많은 책임을 맡다, 한 단계 올라서다; (노력 등을) 강화하다</t>
+          <t>(사업, 프로젝트 등을) 시작하다, 본궤도에 올리다</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>In the absence of the manager, someone needs to step up and lead the team.</t>
+          <t>It took a lot of effort to get the startup off the ground, but it's finally profitable.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>We need to step up our customer service to retain our clients.</t>
+          <t>We need more funding to get this innovative research project off the ground.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ENG-20260527-387</t>
+          <t>ENG-20260527-487</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1651,44 +1651,44 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>back out of</t>
+          <t>lose sleep over</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>/bæk aʊt ɒv/</t>
+          <t>/luːz sliːp ˈoʊvər/</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>약속이나 계약을 취소하다, 손을 떼다</t>
+          <t>~때문에 걱정하여 잠을 못 이루다</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>He tried to back out of the deal at the last minute, but the contract was binding.</t>
+          <t>Don't lose sleep over that minor mistake; it's easily fixable.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>The investor decided to back out of the agreement due to new market conditions.</t>
+          <t>I'm not going to lose sleep over the company's financial results; it's out of my control.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ENG-20260527-388</t>
+          <t>ENG-20260527-488</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1698,44 +1698,44 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>follow through on</t>
+          <t>put a lid on</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>/ˈfɒloʊ θruː ɒn/</t>
+          <t>/pʊt ə lɪd ɒn/</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>약속, 계획 등을 이행하다, 끝까지 실행하다</t>
+          <t>~을 억제하다, 통제하다</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>It's important to follow through on your commitments to build trust with clients.</t>
+          <t>The government tried to put a lid on the rising fuel prices, but it was a challenge.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>She always follows through on her promises, which makes her a reliable leader.</t>
+          <t>We need to put a lid on office gossip before it affects team morale.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ENG-20260527-389</t>
+          <t>ENG-20260527-489</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1750,39 +1750,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>branch out</t>
+          <t>bear fruit</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>/bræntʃ aʊt/</t>
+          <t>/bɛər fruːt/</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>새로운 분야로 진출하다, 사업을 확장하다</t>
+          <t>결실을 맺다, 성과를 내다</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>The tech company decided to branch out into the clean energy sector.</t>
+          <t>After years of hard work, their research project finally began to bear fruit.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>After years in finance, she decided to branch out and start her own consulting firm.</t>
+          <t>Our investment in new technology will eventually bear fruit in increased efficiency.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ENG-20260527-390</t>
+          <t>ENG-20260527-490</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1792,44 +1792,44 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>map out</t>
+          <t>come to terms with</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>/mæp aʊt/</t>
+          <t>/kʌm tə tɜːrmz wɪð/</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>자세하게 계획을 세우다, 설계하다</t>
+          <t>~을 받아들이다, 인정하다 (힘든 현실 등)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>We need to map out a strategy for dealing with the increased competition.</t>
+          <t>She's still trying to come to terms with the unexpected job loss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Before starting the trip, they mapped out their entire route and planned for all contingencies.</t>
+          <t>It's hard to come to terms with the fact that the project failed after all our efforts.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ENG-20260527-391</t>
+          <t>ENG-20260527-491</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1839,44 +1839,44 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>zero in on</t>
+          <t>have a say</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>/ˈzɪəroʊ ɪn ɒn/</t>
+          <t>/hæv ə seɪ/</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>~에 집중하다, ~을 목표로 삼다</t>
+          <t>발언권/결정권을 갖다</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>The investigation will zero in on the specific details of the financial transactions.</t>
+          <t>Every employee should have a say in decisions that affect their work environment.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>The detective managed to zero in on the key suspect after reviewing all the evidence.</t>
+          <t>We believe that customers should have a say in the development of new products.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ENG-20260527-392</t>
+          <t>ENG-20260527-492</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1886,44 +1886,44 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>kick off</t>
+          <t>throw a curveball</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>/kɪk ɒf/</t>
+          <t>/θroʊ ə ˈkɜːrvˌbɔːl/</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>시작하다, 개시하다</t>
+          <t>예상치 못한 문제를 제기하다, 허를 찌르다</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>The conference will kick off with a keynote speech from the CEO.</t>
+          <t>Just when we thought we had everything planned, the client threw us a curveball with a last-minute change.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Let's kick off the meeting by reviewing the agenda.</t>
+          <t>Life has a way of throwing curveballs when you least expect them.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ENG-20260527-393</t>
+          <t>ENG-20260527-493</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1933,44 +1933,44 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>wind down</t>
+          <t>play hardball</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>/waɪnd daʊn/</t>
+          <t>/pleɪ ˈhɑːrdˌbɔːl/</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서서히 끝나다, 마무리하다; 휴식을 취하다</t>
+          <t>강경하게 나가다, 강경책을 쓰다</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>The event will wind down around 5 PM with a networking reception.</t>
+          <t>During the merger negotiations, our CEO decided to play hardball to get the best terms.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>After a busy day, I like to wind down by reading a book.</t>
+          <t>If they refuse to compromise, we might have to play hardball in the next round of talks.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ENG-20260527-394</t>
+          <t>ENG-20260527-494</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1980,44 +1980,44 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>burn out</t>
+          <t>lose one's train of thought</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>/bɜːrn aʊt/</t>
+          <t>/luːz wʌnz treɪn əv θɔːt/</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>(과로 등으로) 기진맥진하다, 소진되다</t>
+          <t>(하던 이야기나 생각을) 놓치다</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Working 80 hours a week can quickly lead to burnout and stress.</t>
+          <t>I was about to tell you something important, but I lost my train of thought.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>She decided to take a sabbatical to avoid burning out from her demanding job.</t>
+          <t>The unexpected question made him lose his train of thought during the presentation.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ENG-20260527-395</t>
+          <t>ENG-20260527-495</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2032,39 +2032,39 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>cash in on</t>
+          <t>put all one's eggs in one basket</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>/kæʃ ɪn ɒn/</t>
+          <t>/pʊt ɔːl wʌnz ɛɡz ɪn wʌn ˈbɑːskɪt/</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>~을 이용해 이득을 얻다, ~로 돈을 벌다</t>
+          <t>모든 것을 한 가지에 걸다, 위험 분산을 하지 않다</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Many companies are trying to cash in on the growing demand for AI technology.</t>
+          <t>It's risky to put all your eggs in one basket when investing; diversify your portfolio.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>They hoped to cash in on the holiday season by offering special discounts.</t>
+          <t>The company decided not to put all its eggs in one basket and explored multiple market segments.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ENG-20260527-396</t>
+          <t>ENG-20260527-496</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2074,44 +2074,44 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>dig in</t>
+          <t>pass the buck</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>/dɪɡ ɪn/</t>
+          <t>/pɑːs ðə bʌk/</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>열심히 먹기 시작하다; 굳게 버티다, 고수하다</t>
+          <t>책임을 전가하다, 떠넘기다</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>When the food arrived, everyone started to dig in with enthusiasm.</t>
+          <t>Don't try to pass the buck; you're responsible for this mistake.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Despite the opposition, the politician dug in and refused to change his stance.</t>
+          <t>Good leaders don't pass the buck; they take responsibility.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ENG-20260527-397</t>
+          <t>ENG-20260527-497</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2121,44 +2121,44 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>get ahead</t>
+          <t>talk shop</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>/ɡɛt əˈhɛd/</t>
+          <t>/tɔːk ʃɒp/</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>성공하다, 앞서나가다</t>
+          <t>일/직업 이야기를 하다 (특히 사적인 자리에서)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Many international students find it harder to get ahead in the US job market.</t>
+          <t>We were at a party, but all they did was talk shop about the latest tech trends.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>To get ahead in this industry, you need to be constantly learning new skills.</t>
+          <t>I tried to enjoy my vacation, but my colleagues kept wanting to talk shop.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ENG-20260527-398</t>
+          <t>ENG-20260527-498</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2173,39 +2173,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>get by</t>
+          <t>bend over backwards</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>/ɡɛt baɪ/</t>
+          <t>/bɛnd ˈoʊvər ˈbækˌwɜːrdz/</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>그럭저럭 살아가다, 근근이 생활하다</t>
+          <t>엄청나게 노력하다, 무척 애쓰다</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>With prices rising, it's becoming harder for families to get by on a single income.</t>
+          <t>We bent over backwards to meet the client's demands, but they were still unhappy.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>I don't earn much, but I manage to get by with careful budgeting.</t>
+          <t>Our customer support team will bend over backwards to resolve your issue.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ENG-20260527-399</t>
+          <t>ENG-20260527-499</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2220,39 +2220,39 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>give in</t>
+          <t>go with one's gut</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>/ɡɪv ɪn/</t>
+          <t>/ɡoʊ wɪð wʌnz ɡʌt/</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>양보하다, 굴복하다</t>
+          <t>직감에 따르다, 본능적으로 행동하다</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>After hours of debate, the opposing party finally gave in and accepted the proposal.</t>
+          <t>I wasn't sure what to do, but I decided to go with my gut feeling and it paid off.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>My kids kept asking for ice cream until I finally gave in.</t>
+          <t>Sometimes, in uncertain situations, it's best to go with your gut rather than overthinking.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ENG-20260527-400</t>
+          <t>ENG-20260527-500</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2262,44 +2262,44 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>give up on</t>
+          <t>get one's foot in the door</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>/ɡɪv ʌp ɒn/</t>
+          <t>/ɡɛt wʌnz fʊt ɪn ðə dɔːr/</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>~을 포기하다, ~에 대한 희망을 버리다</t>
+          <t>(직업, 분야에) 발판을 마련하다, 첫발을 들여놓다</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Don't give up on your American dream, even if the job market is tough.</t>
+          <t>He started as an intern, just trying to get his foot in the door at the prestigious firm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>We can't give up on finding a solution to this problem, no matter how difficult it seems.</t>
+          <t>An entry-level position is often a good way to get your foot in the door of a competitive industry.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ENG-20260527-401</t>
+          <t>ENG-20260527-501</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2314,39 +2314,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>grow on</t>
+          <t>off the top of one's head</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>/ɡroʊ ɒn/</t>
+          <t>/ɒf ðə tɒp ɒv wʌnz hɛd/</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>점점 더 좋아지다, 마음에 들게 되다</t>
+          <t>즉석에서, 생각나는 대로</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>At first, I didn't like the new office design, but it's starting to grow on me.</t>
+          <t>I can't give you the exact figures off the top of my head, but I can look them up.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>The new song wasn't my favorite initially, but it really started to grow on me after a few listens.</t>
+          <t>Off the top of my head, I'd say the main issue is communication.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ENG-20260527-402</t>
+          <t>ENG-20260527-502</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2361,39 +2361,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>hand over</t>
+          <t>hit the nail on the head</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>/hænd ˈoʊvər/</t>
+          <t>/hɪt ðə neɪl ɒn ðə hɛd/</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>넘겨주다, 양도하다</t>
+          <t>정확히 핵심을 짚다, 정곡을 찌르다</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>The outgoing CEO will hand over his responsibilities to his successor next month.</t>
+          <t>Your analysis of the problem really hit the nail on the head.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>The company decided to hand over its operations to a local partner in the region.</t>
+          <t>When you said the main challenge was motivation, you really hit the nail on the head.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ENG-20260527-403</t>
+          <t>ENG-20260527-503</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2408,39 +2408,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>knock off</t>
+          <t>blow off steam</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>/nɒk ɒf/</t>
+          <t>/bloʊ ɒf stiːm/</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>일을 마치다, 퇴근하다; 가격을 깎다; 빠르게 만들다/생산하다</t>
+          <t>스트레스를 풀다, 울분을 터뜨리다</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>We can probably knock off early if we finish all our tasks by lunchtime.</t>
+          <t>After a long week at work, he liked to go to the gym to blow off steam.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Can you knock off 10% from the price if I buy two items?</t>
+          <t>Let's go for a walk to blow off some steam after that tense meeting.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ENG-20260527-404</t>
+          <t>ENG-20260527-504</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2450,44 +2450,44 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>lay off</t>
+          <t>take a toll on</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>/leɪ ɒf/</t>
+          <t>/teɪk ə toʊl ɒn/</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>(직원을) 해고하다, 일시 해고하다</t>
+          <t>~에 큰 피해를 주다, 악영향을 미치다</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Due to decreased demand, the factory had to lay off a significant number of workers.</t>
+          <t>The stress of the job started to take a toll on his health.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>The struggling startup had to lay off a third of its staff to stay afloat.</t>
+          <t>The prolonged economic downturn is taking a toll on small businesses.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ENG-20260527-405</t>
+          <t>ENG-20260527-505</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2497,44 +2497,44 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>let down</t>
+          <t>think outside the box</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>/lɛt daʊn/</t>
+          <t>/θɪŋk aʊtˈsaɪd ðə bɒks/</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>실망시키다, 저버리다</t>
+          <t>고정관념에서 벗어나 사고하다, 창의적으로 생각하다</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>I hope I don't let down my team with my performance in the upcoming presentation.</t>
+          <t>To solve this complex problem, we need to think outside the box and come up with new solutions.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>She felt completely let down by her friend who didn't show up.</t>
+          <t>The company encourages employees to think outside the box for innovative product ideas.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ENG-20260527-406</t>
+          <t>ENG-20260527-506</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2544,44 +2544,44 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>live up to</t>
+          <t>bring to the table</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>/lɪv ʌp tuː/</t>
+          <t>/brɪŋ tə ðə ˈteɪbl/</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>(기대, 명성 등에) 부응하다, 부합하다</t>
+          <t>제공하다, 기여하다 (논의, 협상 등에서)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>The new product needs to live up to the high expectations set by its marketing campaign.</t>
+          <t>What new skills can you bring to the table if you join our team?</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>The movie didn't quite live up to the hype, but it was still entertaining.</t>
+          <t>Each department will bring their ideas to the table during the strategic planning session.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ENG-20260527-407</t>
+          <t>ENG-20260527-507</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2591,44 +2591,44 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>make for</t>
+          <t>put one's two cents in</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>/meɪk fɔːr/</t>
+          <t>/pʊt wʌnz tuː sɛnts ɪn/</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>~쪽으로 가다; ~에 도움이 되다, ~을 야기하다</t>
+          <t>자기 의견을 말하다, 한마디 거들다 (주로 비공식적이고 겸손한 표현)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>The rising prices will make for increased financial stress for many families.</t>
+          <t>If I may put my two cents in, I think we should reconsider the budget.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>A strong team spirit makes for a productive work environment.</t>
+          <t>Everyone was discussing the new policy, so I decided to put my two cents in.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ENG-20260527-408</t>
+          <t>ENG-20260527-508</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2643,39 +2643,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>make up for</t>
+          <t>take the plunge</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>/meɪk ʌp fɔːr/</t>
+          <t>/teɪk ðə plʌndʒ/</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>~을 만회하다, 보충하다; ~을 보상하다</t>
+          <t>과감히 시도하다, 중요한 결정을 내리다</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>He tried to make up for his mistake by working extra hours over the weekend.</t>
+          <t>After months of hesitation, she finally decided to take the plunge and start her own business.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>The free dessert didn't really make up for the terrible service we received.</t>
+          <t>I'm nervous about moving to a new city, but it's time to take the plunge.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ENG-20260527-409</t>
+          <t>ENG-20260527-509</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2685,44 +2685,44 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>miss out on</t>
+          <t>have a change of heart</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>/mɪs aʊt ɒn/</t>
+          <t>/hæv ə tʃeɪndʒ əv hɑːrt/</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>~을 놓치다, ~에 참여하지 못하다</t>
+          <t>마음을 바꾸다, 변심하다</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Don't miss out on the opportunity to invest in these booming AI chip stocks.</t>
+          <t>He was going to sell his car, but he had a change of heart at the last minute.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>I'd hate to miss out on the annual company picnic this year.</t>
+          <t>The board had a change of heart and decided to approve the controversial merger.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ENG-20260527-410</t>
+          <t>ENG-20260527-510</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2732,44 +2732,44 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>pass up</t>
+          <t>get one's act together</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>/pæs ʌp/</t>
+          <t>/ɡɛt wʌnz ækt təˈɡɛðər/</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>~을 거절하다, ~을 놓치다</t>
+          <t>정신 차리다, 일을 제대로 하다</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>She couldn't pass up the chance to work at such a prestigious company.</t>
+          <t>If you don't get your act together, you're going to lose your job.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>It's a great opportunity, you shouldn't pass it up.</t>
+          <t>The team needs to get its act together before the final presentation.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ENG-20260527-411</t>
+          <t>ENG-20260527-511</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2779,44 +2779,44 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>pick up on</t>
+          <t>run a tight ship</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>/pɪk ʌp ɒn/</t>
+          <t>/rʌn ə taɪt ʃɪp/</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>~을 알아채다, 눈치채다</t>
+          <t>조직/사업을 엄격하고 효율적으로 운영하다</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>He didn't directly say it, but I picked up on the fact that he wasn't happy with the decision.</t>
+          <t>The new manager runs a very tight ship, ensuring everything is organized and efficient.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>She's very observant and always picks up on subtle changes in people's moods.</t>
+          <t>Our finance department runs a tight ship, which is why we rarely have budget overruns.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ENG-20260527-412</t>
+          <t>ENG-20260527-512</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2826,44 +2826,44 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>point out</t>
+          <t>pull one's weight</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>/pɔɪnt aʊt/</t>
+          <t>/pʊl wʌnz weɪt/</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>지적하다, 언급하다</t>
+          <t>자기 몫을 다하다, 책임을 다하다</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>The expert pointed out that the AI rally might not last forever.</t>
+          <t>Everyone on the team needs to pull their weight for us to succeed.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>The teacher pointed out several errors in my essay.</t>
+          <t>He's not pulling his weight in the group project, which is affecting our progress.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ENG-20260527-413</t>
+          <t>ENG-20260527-513</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2878,39 +2878,39 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>read into</t>
+          <t>rock the boat</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>/riːd ˈɪntuː/</t>
+          <t>/rɒk ðə boʊt/</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>(숨겨진 의미를) 지나치게 확대 해석하다</t>
+          <t>평지풍파를 일으키다, 말썽을 일으키다</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Don't read too much into his comments; he's probably just tired.</t>
+          <t>I don't want to rock the boat by bringing up that controversial topic again.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>She tends to read into every little gesture, looking for hidden meanings.</t>
+          <t>The new employee was advised not to rock the boat too much in her first few months.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ENG-20260527-414</t>
+          <t>ENG-20260527-514</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2920,44 +2920,44 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>root for</t>
+          <t>have one's work cut out for one</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>/ruːt fɔːr/</t>
+          <t>/hæv wʌnz wɜːrk kʌt aʊt fɔːr wʌn/</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>~을 응원하다, 지지하다</t>
+          <t>할 일이 많다, 어려운 과제가 주어지다</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>I'm always rooting for the underdog in any competition.</t>
+          <t>With all these new regulations, the compliance team really has its work cut out for it.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Our whole family is rooting for you to win the championship.</t>
+          <t>After the merger, the integration team will have their work cut out for them.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ENG-20260527-415</t>
+          <t>ENG-20260527-515</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2972,39 +2972,39 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>rub off on</t>
+          <t>get the hang of</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>/rʌb ɒf ɒn/</t>
+          <t>/ɡɛt ðə hæŋ ɒv/</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>(특성, 습관 등이) ~에게 전염되다, 영향을 주다</t>
+          <t>~의 요령을 터득하다, 익숙해지다</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Her enthusiasm for the project eventually started to rub off on the rest of the team.</t>
+          <t>It took me a few tries, but I'm finally getting the hang of this new software.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>I hope some of your good study habits rub off on me.</t>
+          <t>Don't worry if it's difficult at first; you'll get the hang of it with practice.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ENG-20260527-416</t>
+          <t>ENG-20260527-516</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>set out</t>
+          <t>talk someone into</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3029,29 +3029,29 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>/sɛt aʊt/</t>
+          <t>/tɔːk ˈsʌmwʌn ˈɪntuː/</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>출발하다; (목표를 가지고) 시작하다; 진술하다, 제시하다</t>
+          <t>~을 설득하여 ~하게 하다</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>The new initiative sets out clear guidelines for ethical AI development.</t>
+          <t>She didn't want to go, but I managed to talk her into joining us for dinner.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>They set out to build the most innovative smartphone on the market.</t>
+          <t>We need to talk the client into extending the deadline.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ENG-20260527-417</t>
+          <t>ENG-20260527-517</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>size up</t>
+          <t>talk someone out of</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3076,29 +3076,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>/saɪz ʌp/</t>
+          <t>/tɔːk ˈsʌmwʌn aʊt ɒv/</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>평가하다, 상황을 판단하다</t>
+          <t>~을 설득하여 ~하지 못하게 하다</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>The investors are trying to size up the potential risks of the new venture.</t>
+          <t>I tried to talk him out of quitting his job, but he had already made up his mind.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Before making a move, it's always good to size up your opponent.</t>
+          <t>Can you talk your boss out of cutting the marketing budget?</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ENG-20260527-418</t>
+          <t>ENG-20260527-518</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3108,44 +3108,44 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>stand out</t>
+          <t>put someone on the spot</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>/stænd aʊt/</t>
+          <t>/pʊt ˈsʌmwʌn ɒn ðə spɒt/</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>눈에 띄다, 두드러지다</t>
+          <t>~를 곤란한 입장에 빠뜨리다, 즉답을 요구하다</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Her unique presentation really made her stand out among the other candidates.</t>
+          <t>The reporter's unexpected question put the politician on the spot.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>To get noticed in a crowded market, your product needs to stand out.</t>
+          <t>I didn't want to put you on the spot, but I need an answer by tomorrow.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ENG-20260527-419</t>
+          <t>ENG-20260527-519</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3155,44 +3155,44 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>stir up</t>
+          <t>have a thick skin</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>/stɜːr ʌp/</t>
+          <t>/hæv ə θɪk skɪn/</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>(문제, 감정 등을) 불러일으키다, 자극하다</t>
+          <t>남의 비판에 개의치 않다, 맷집이 좋다</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>His controversial comments stirred up a lot of debate on social media.</t>
+          <t>In this industry, you need to have a thick skin because criticism is frequent.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Don't stir up trouble by talking about sensitive topics at the family dinner.</t>
+          <t>You need to have a thick skin if you're going to work in sales.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ENG-20260527-420</t>
+          <t>ENG-20260527-520</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3207,39 +3207,39 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>string along</t>
+          <t>have a thin skin</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>/strɪŋ əˈlɒŋ/</t>
+          <t>/hæv ə θɪn skɪn/</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>~을 속이다, ~을 희망 고문하다</t>
+          <t>감성적이다, 상처를 잘 받다</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>I feel like they're just stringing me along with promises of a promotion.</t>
+          <t>She has a thin skin, so be careful with your comments around her.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>She realized her ex-boyfriend was just stringing her along and never intended to get serious.</t>
+          <t>He's a talented artist, but he has a thin skin when it comes to criticism of his work.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ENG-20260527-421</t>
+          <t>ENG-20260527-521</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3249,44 +3249,44 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>take on</t>
+          <t>make a long story short</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>/teɪk ɒn/</t>
+          <t>/meɪk ə lɒŋ stɔːri ʃɔːrt/</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>책임을 맡다; (도전, 임무 등을) 받아들이다; (직원을) 고용하다</t>
+          <t>요약하자면, 간단히 말해서</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>She was hesitant to take on such a challenging role, but she eventually accepted.</t>
+          <t>To make a long story short, we ended up missing our flight.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>The company decided to take on five new interns for the summer.</t>
+          <t>Long story short, the project was successful but incredibly challenging.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ENG-20260527-422</t>
+          <t>ENG-20260527-522</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3301,39 +3301,39 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>talk out of</t>
+          <t>get bent out of shape</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>/tɔːk aʊt ɒv/</t>
+          <t>/ɡɛt bɛnt aʊt əv ʃeɪp/</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>~에게 설득하여 ~을 하지 못하게 하다</t>
+          <t>화내다, 몹시 기분 상하다</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>His friends tried to talk him out of quitting his stable job.</t>
+          <t>Don't get bent out of shape over a minor disagreement; it's not worth it.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>I managed to talk her out of buying that expensive dress she didn't need.</t>
+          <t>He got all bent out of shape when I told him the meeting was rescheduled.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ENG-20260527-423</t>
+          <t>ENG-20260527-523</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3343,44 +3343,44 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>tell apart</t>
+          <t>take a stand</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>/tɛl əˈpɑːrt/</t>
+          <t>/teɪk ə stænd/</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>~을 구별하다, 분간하다</t>
+          <t>입장을 취하다, 태도를 분명히 하다</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>The twins look so similar; it's hard to tell them apart.</t>
+          <t>The company decided to take a stand against child labor in their supply chain.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>The two product models are so similar that only an expert can tell them apart.</t>
+          <t>It's important to take a stand on ethical issues, even if it's unpopular.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ENG-20260527-424</t>
+          <t>ENG-20260527-524</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3390,44 +3390,44 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>throw off</t>
+          <t>step up to the plate</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>/θroʊ ɒf/</t>
+          <t>/stɛp ʌp tuː ðə pleɪt/</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>혼란스럽게 하다, 방해하다; (냄새, 열 등을) 내뿜다</t>
+          <t>책임을 맡다, 적극적으로 나서다</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>The sudden change in the schedule threw off my entire day.</t>
+          <t>When the team leader quit, John stepped up to the plate and took charge.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>The unexpected question completely threw him off during the interview.</t>
+          <t>We need someone who is willing to step up to the plate and lead this initiative.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ENG-20260527-425</t>
+          <t>ENG-20260527-525</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3442,39 +3442,39 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>touch on</t>
+          <t>pay dividends</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>/tʌtʃ ɒn/</t>
+          <t>/peɪ ˈdɪvɪdɛndz/</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>(주제 등을) 간단히 다루다, 언급하다</t>
+          <t>수익을 내다, 이득을 가져다주다</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>The speaker briefly touched on the economic implications of the new policy.</t>
+          <t>Investing in employee training always pays dividends in the long run.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>During the meeting, we only had time to touch on the main points.</t>
+          <t>Her dedication and hard work eventually paid dividends with a promotion.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ENG-20260527-426</t>
+          <t>ENG-20260527-526</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3484,44 +3484,44 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>walk out on</t>
+          <t>get a foot in the door</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>/wɔːk aʊt ɒn/</t>
+          <t>/ɡɛt ə fʊt ɪn ðə dɔːr/</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>~을 버리다, 갑자기 떠나다</t>
+          <t>(특정 직업/조직에) 발판을 마련하다, 첫발을 들여놓다</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>He walked out on his family without saying a word, leaving them in financial difficulty.</t>
+          <t>He started as an intern, just trying to get his foot in the door at the prestigious firm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>It was unprofessional for him to walk out on the project halfway through.</t>
+          <t>An entry-level position is often a good way to get your foot in the door of a competitive industry.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ENG-20260527-427</t>
+          <t>ENG-20260527-527</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3531,44 +3531,44 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>zone out</t>
+          <t>put someone through the wringer</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>/zoʊn aʊt/</t>
+          <t>/pʊt ˈsʌmwʌn θruː ðə ˈrɪŋər/</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>멍하니 있다, 집중하지 못하다</t>
+          <t>몹시 힘들게 하다, 고통을 주다</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>During the long lecture, I found myself zoning out and thinking about dinner.</t>
+          <t>The audit really put our finance department through the wringer last month.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Sometimes I just zone out when I'm tired and need a break.</t>
+          <t>The rigorous training program put the new recruits through the wringer.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ENG-20260527-428</t>
+          <t>ENG-20260527-528</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3578,44 +3578,44 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>drum up business</t>
+          <t>at the end of the day</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>/drʌm ʌp ˈbɪznɪs/</t>
+          <t>/æt ðɪ ɛnd əv ðə deɪ/</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>손님을 모으다, 사업을 활성화하다</t>
+          <t>결국에는, 궁극적으로는</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>The new cafe is using social media to drum up business in the neighborhood.</t>
+          <t>We can argue about the details, but at the end of the day, we all want the project to succeed.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>We need to come up with new strategies to drum up business during the off-peak season.</t>
+          <t>At the end of the day, customer satisfaction is our top priority.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ENG-20260527-429</t>
+          <t>ENG-20260527-529</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>go the extra mile</t>
+          <t>come to a head</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3640,29 +3640,29 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>/ɡoʊ ðɪ ˈɛkstrə maɪl/</t>
+          <t>/kʌm tuː ə hɛd/</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>특별히 더 노력하다, 최선을 다하다</t>
+          <t>극에 달하다, 절정에 이르다 (위기나 문제 등)</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Our customer service team always goes the extra mile to ensure customer satisfaction.</t>
+          <t>The ongoing tensions between the two departments finally came to a head last week.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>To get that promotion, you'll really need to go the extra mile and impress your boss.</t>
+          <t>The dispute over funding came to a head during the board meeting.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ENG-20260527-430</t>
+          <t>ENG-20260527-530</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>put out feelers</t>
+          <t>get a grasp of</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3687,29 +3687,29 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>/pʊt aʊt ˈfiːlərz/</t>
+          <t>/ɡɛt ə ɡrɑːsp ɒv/</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>탐색하다, 의향을 타진하다</t>
+          <t>~을 이해하다, 파악하다</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Before launching the new product, we need to put out feelers to gauge market interest.</t>
+          <t>It took him a while to get a good grasp of the complex economic theory.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>I'm putting out feelers for a new job, quietly seeing what opportunities are available.</t>
+          <t>New employees need time to get a full grasp of the company's internal processes.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ENG-20260527-431</t>
+          <t>ENG-20260527-531</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>keep an eye on</t>
+          <t>keep tabs on</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3734,29 +3734,29 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>/kiːp ən aɪ ɒn/</t>
+          <t>/kiːp tæbz ɒn/</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>~을 주시하다, ~을 잘 살피다</t>
+          <t>~을 주시하다, 감시하다</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Please keep an eye on the market trends while I'm away.</t>
+          <t>The manager asked me to keep tabs on the new project's progress.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Can you keep an eye on my bag while I go to the restroom?</t>
+          <t>It's important to keep tabs on your competitors' strategies.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ENG-20260527-432</t>
+          <t>ENG-20260527-532</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3766,12 +3766,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>make a point</t>
+          <t>take a backseat</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3781,29 +3781,29 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>/meɪk ə pɔɪnt/</t>
+          <t>/teɪk ə ˈbækˌsiːt/</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>(특정 사실을) 강조하다, 역설하다</t>
+          <t>덜 중요한 역할을 하다, 뒷전으로 물러나다</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>She made a point of thanking every member of her team for their hard work.</t>
+          <t>After years of leading, she decided to take a backseat and let younger colleagues take charge.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>During the presentation, he made a point to highlight the company's achievements.</t>
+          <t>Sometimes you need to take a backseat and let others lead.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ENG-20260527-433</t>
+          <t>ENG-20260527-533</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>turn a blind eye</t>
+          <t>put a spin on</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3828,29 +3828,29 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>/tɜːrn ə blaɪnd aɪ/</t>
+          <t>/pʊt ə spɪn ɒn/</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>못 본 척하다, 눈감아주다</t>
+          <t>(정보, 상황 등을) 유리하게 해석/설명하다, (견해를) 가미하다</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>The management was accused of turning a blind eye to the bullying behavior.</t>
+          <t>The politician tried to put a positive spin on the negative election results.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>You can't just turn a blind eye to the problems in our community.</t>
+          <t>PR teams often try to put a favorable spin on bad news.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ENG-20260527-434</t>
+          <t>ENG-20260527-534</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Modern Family</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>pull rank</t>
+          <t>break the ice</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3875,29 +3875,29 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>/pʊl ræŋk/</t>
+          <t>/breɪk ðɪ aɪs/</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>직위나 권한을 내세워 지시하다</t>
+          <t>딱딱한 분위기를 깨다, 서먹서먹한 관계를 완화하다</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Instead of debating, the manager just pulled rank and made a unilateral decision.</t>
+          <t>We played a few games to break the ice at the beginning of the workshop.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Don't try to pull rank on me; we're all equals in this project.</t>
+          <t>A funny anecdote is always a good way to break the ice in a presentation.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ENG-20260527-435</t>
+          <t>ENG-20260527-535</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>pay lip service</t>
+          <t>put one's money where one's mouth is</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3922,29 +3922,29 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>/peɪ lɪp ˈsɜːrvɪs/</t>
+          <t>/pʊt wʌnz ˈmʌni wɛər wʌnz maʊθ ɪz/</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>겉으로만 동의하거나 지지하는 척하다, 입발림을 하다</t>
+          <t>말뿐이 아니라 행동으로 보여주다, 공언한 대로 돈을 쓰거나 행동하다</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Critics argue that the company only pays lip service to environmental protection without real action.</t>
+          <t>He keeps saying he'll invest, but he needs to put his money where his mouth is.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Many politicians pay lip service to helping the poor but do little in practice.</t>
+          <t>If the company truly believes in environmental protection, they need to put their money where their mouth is and invest in sustainable practices.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ENG-20260527-436</t>
+          <t>ENG-20260527-536</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3954,44 +3954,44 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>give someone the green light</t>
+          <t>on the same wavelength</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>/ɡɪv ˌsʌmwʌn ðə ɡriːn laɪt/</t>
+          <t>/ɒn ðə seɪm ˈweɪvlɛŋθ/</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>~에게 허락하다, 승인하다</t>
+          <t>생각이 일치하는, 통하는</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>The board finally gave the team the green light to proceed with the experimental project.</t>
+          <t>My colleague and I are always on the same wavelength when it comes to creative ideas.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Once we get the green light from legal, we can start advertising the new service.</t>
+          <t>It helps a lot when you're working with someone who's on the same wavelength.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ENG-20260527-437</t>
+          <t>ENG-20260527-537</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>give someone the benefit of the doubt</t>
+          <t>throw one's weight around</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4016,29 +4016,29 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>/ɡɪv ˌsʌmwʌn ðə ˈbɛnɪfɪt ɒv ðə daʊt/</t>
+          <t>/θroʊ wʌnz weɪt əˈraʊnd/</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>일단 믿어주다, 좋게 봐주다</t>
+          <t>권력을 휘두르다, 위세를 부리다</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Despite the mixed reviews, I decided to give the new restaurant the benefit of the doubt.</t>
+          <t>The new manager started throwing his weight around, making everyone uncomfortable.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>He's usually very reliable, so I'll give him the benefit of the doubt about being late today.</t>
+          <t>Don't throw your weight around just because you got a promotion; it's bad for team morale.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ENG-20260527-438</t>
+          <t>ENG-20260527-538</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4048,12 +4048,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>break the bank</t>
+          <t>cut someone some slack</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4063,29 +4063,29 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>/breɪk ðə bæŋk/</t>
+          <t>/kʌt ˈsʌmwʌn sʌm slæk/</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>엄청난 돈을 쓰다, 거액을 지출하다</t>
+          <t>~에게 너그러이 대하다, ~을 봐주다</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Getting better WiFi for hundreds of trains shouldn't break the bank for the government.</t>
+          <t>He's been under a lot of stress lately, so cut him some slack.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>We want a nice vacation, but we don't want to break the bank.</t>
+          <t>It's her first day, so we should cut her some slack if she makes mistakes.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ENG-20260527-439</t>
+          <t>ENG-20260527-539</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4095,44 +4095,44 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>foot the bill</t>
+          <t>get off the hook</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>/fʊt ðə bɪl/</t>
+          <t>/ɡɛt ɒf ðə hʊk/</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>계산하다, 비용을 부담하다</t>
+          <t>(어려운 상황, 책임에서) 벗어나다</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>The government will foot the bill for the WiFi upgrade on the trains.</t>
+          <t>I thought I'd have to work late, but luckily I got off the hook.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>My company offered to foot the bill for my further education.</t>
+          <t>The company managed to get off the hook for the environmental damage by settling out of court.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ENG-20260527-440</t>
+          <t>ENG-20260527-540</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>piece of cake</t>
+          <t>give it one's best shot</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4157,29 +4157,29 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>/piːs ɒv keɪk/</t>
+          <t>/ɡɪv ɪt wʌnz bɛst ʃɒt/</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>매우 쉬운 일</t>
+          <t>최선을 다하다</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Don't worry about the exam; it'll be a piece of cake if you've studied.</t>
+          <t>I might not win, but I'm going to give it my best shot in the competition.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Learning to use the new software was a piece of cake for him.</t>
+          <t>Even if the odds are against us, we should still give it our best shot.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ENG-20260527-441</t>
+          <t>ENG-20260527-541</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>back to the drawing board</t>
+          <t>on the fly</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4204,29 +4204,29 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>/bæk tuː ðə ˈdrɔːɪŋ bɔːrd/</t>
+          <t>/ɒn ðə flaɪ/</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>원점으로 돌아가 다시 시작하다</t>
+          <t>즉석에서, 즉흥적으로</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Our first attempt failed, so it's back to the drawing board for the entire team.</t>
+          <t>We had to make some crucial decisions on the fly during the crisis.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>The client rejected our proposal, so we're back to the drawing board to come up with new ideas.</t>
+          <t>The developer had to fix the bug on the fly during the live demo.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ENG-20260527-442</t>
+          <t>ENG-20260527-542</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>jump on the bandwagon</t>
+          <t>the last straw</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4251,29 +4251,29 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>/dʒʌmp ɒn ðə ˈbændˌwæɡən/</t>
+          <t>/ðə læst strɔː/</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>시류에 편승하다, 유행을 따르다</t>
+          <t>더 이상 참을 수 없는 한계, 마지막 지푸라기</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Many investors are jumping on the AI bandwagon hoping for quick profits.</t>
+          <t>His constant tardiness was annoying, but breaking my laptop was the last straw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>After seeing the success of their competitor, they decided to jump on the bandwagon and offer similar services.</t>
+          <t>The increasing energy bills were the last straw for many low-income households.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ENG-20260527-443</t>
+          <t>ENG-20260527-543</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4288,39 +4288,39 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>get a handle on</t>
+          <t>have a stake in</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>/ɡɛt ə ˈhændl ɒn/</t>
+          <t>/hæv ə steɪk ɪn/</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>~을 이해하고 통제하다, 다루는 방법을 알다</t>
+          <t>~에 이해관계가 있다, ~에 대한 책임/권리가 있다</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>It took me a while to get a handle on the new software's features.</t>
+          <t>As shareholders, we all have a stake in the company's success.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>We need to get a handle on our expenses before they get out of control.</t>
+          <t>Every team member has a stake in the project's outcome.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ENG-20260527-444</t>
+          <t>ENG-20260527-544</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>have a lot on one's plate</t>
+          <t>lose one's cool</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4345,29 +4345,29 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>/hæv ə lɒt ɒn wʌnz pleɪt/</t>
+          <t>/luːz wʌnz kuːl/</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>할 일이 많다, 책임이 많다</t>
+          <t>침착함을 잃다, 화내다</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>With the upcoming merger and new product launch, the CEO has a lot on her plate.</t>
+          <t>He rarely loses his cool, even under immense pressure.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>I can't take on any more tasks right now; I already have a lot on my plate.</t>
+          <t>It's easy to lose your cool when dealing with difficult customers.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ENG-20260527-445</t>
+          <t>ENG-20260527-545</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4377,44 +4377,44 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>keep one's head above water</t>
+          <t>take sides</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>/kiːp wʌnz hɛd əˈbʌv ˈwɔːtər/</t>
+          <t>/teɪk saɪdz/</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>빚지지 않고 겨우 살아가다, 재정적 어려움 속에서 버티다</t>
+          <t>(논쟁 등에서) 편을 들다</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Many small businesses are struggling to keep their heads above water during the economic downturn.</t>
+          <t>In a dispute between friends, it's often best not to take sides.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>With rising inflation, it's hard for single parents to keep their heads above water.</t>
+          <t>The manager refused to take sides in the argument between the two employees.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ENG-20260527-446</t>
+          <t>ENG-20260527-546</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4424,44 +4424,44 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>up in the air</t>
+          <t>give every chance to succeed</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>/ʌp ɪn ðɪ ɛər/</t>
+          <t>/ɡɪv ˈɛvri tʃæns tuː səkˈsiːd/</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>미정인, 불확실한</t>
+          <t>~에게 성공할 모든 기회를 주다</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Our travel plans for the summer are still up in the air due to the uncertain situation.</t>
+          <t>U.S. will give Iran talks 'every chance to succeed'</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>The future of the project is still up in the air, awaiting board approval.</t>
+          <t>The company decided to give the new startup every chance to succeed by providing ample resources.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ENG-20260527-447</t>
+          <t>ENG-20260527-547</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4471,44 +4471,44 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Modern Family</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>a drop in the bucket</t>
+          <t>near a deal</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>/ə drɒp ɪn ðə ˈbʌkɪt/</t>
+          <t>/nɪər ə diːl/</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>새 발의 피, 극히 일부에 지나지 않는 양</t>
+          <t>합의에 근접하다</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>The initial investment was just a drop in the bucket compared to the total cost of the project.</t>
+          <t>traders assess whether U.S. is nearing a deal with Iran</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Our contribution to the charity felt like a drop in the bucket, but every bit helps.</t>
+          <t>After weeks of intense negotiations, both parties finally seem to be nearing a deal.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ENG-20260527-448</t>
+          <t>ENG-20260527-548</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>actions speak louder than words</t>
+          <t>be the right way to go</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4533,29 +4533,29 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>/ˈækʃənz spiːk ˈlaʊdər ðæn wɜːrdz/</t>
+          <t>/bi ðə raɪt weɪ tuː ɡoʊ/</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>말보다 행동이 더 중요하다</t>
+          <t>올바른/최적의 방법이다</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>He keeps promising to change, but actions speak louder than words.</t>
+          <t>the automaker's decision to kill its EV to focus on plug-in hybrid electric vehicles was 'the right way to go' for his company.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Instead of just talking about sustainability, the company showed that actions speak louder than words with its new eco-friendly products.</t>
+          <t>Investing in sustainable energy is definitely the right way to go for future economic growth.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ENG-20260527-449</t>
+          <t>ENG-20260527-549</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4565,44 +4565,44 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Modern Family</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>add fuel to the fire</t>
+          <t>dilute the vote</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>/æd fjuːəl tuː ðə ˈfaɪər/</t>
+          <t>/daɪˈluːt ðə voʊt/</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>불난 집에 부채질하다, 상황을 악화시키다</t>
+          <t>(특정 집단의) 표의 영향력을 약화시키다</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>His sarcastic remark only added fuel to the fire during the heated discussion.</t>
+          <t>congressional map that dilutes Black vote</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Don't mention the layoffs, you'll just add fuel to the fire of employee discontent.</t>
+          <t>Critics argued that the new district boundaries would dilute the vote of minority communities.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ENG-20260527-450</t>
+          <t>ENG-20260527-550</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4612,44 +4612,44 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>all in the same boat</t>
+          <t>feel worse off</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>/ɔːl ɪn ðə seɪm boʊt/</t>
+          <t>/fiːl wɜːrs ɔːf/</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>모두 같은 처지에 있다, 한 배를 타다</t>
+          <t>형편이 더 나빠졌다고 느끼다</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>With rising inflation, we're all in the same boat, trying to cut down on expenses.</t>
+          <t>Americans feel worse off than ever before</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>During the pandemic, remote workers and office workers were all in the same boat, adapting to new routines.</t>
+          <t>Many low-income families feel worse off due to the rising cost of living.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ENG-20260527-451</t>
+          <t>ENG-20260527-551</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>barking up the wrong tree</t>
+          <t>when the pinch comes</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4674,29 +4674,29 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>/ˈbɑːrkɪŋ ʌp ðə rɒŋ triː/</t>
+          <t>/wɛn ðə pɪntʃ kʌmz/</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>엉뚱한 사람을 비난하거나 엉뚱한 방향으로 추측하다</t>
+          <t>어려움/곤궁이 닥칠 때</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>If you think I'm responsible for this mistake, you're barking up the wrong tree.</t>
+          <t>action now can save money when the pinch comes this winter.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>The police were barking up the wrong tree until they found new evidence.</t>
+          <t>It's wise to save some money for a rainy day, especially for when the pinch comes.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ENG-20260527-452</t>
+          <t>ENG-20260527-552</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4706,44 +4706,44 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>by the book</t>
+          <t>return to normal</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>/baɪ ðə bʊk/</t>
+          <t>/rɪˈtɜːrn tuː ˈnɔːrməl/</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>규칙대로, 원칙대로</t>
+          <t>정상으로 돌아오다</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>The auditors always do everything by the book, leaving no room for error.</t>
+          <t>Iran could return the passageway to normal traffic flows within a month of a peace deal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>We have to handle this situation strictly by the book to avoid any legal issues.</t>
+          <t>After the power outage, it took a few hours for services to return to normal.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ENG-20260527-453</t>
+          <t>ENG-20260527-553</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4753,44 +4753,44 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Modern Family</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>come hell or high water</t>
+          <t>be under intense pressure</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>/kʌm hɛl ɔːr haɪ ˈwɔːtər/</t>
+          <t>/bi ˈʌndər ɪnˈtɛns ˈprɛʃər/</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>어떤 어려움이 있어도, 무슨 수를 써서라도</t>
+          <t>엄청난 압력을 받다</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Come hell or high water, we will finish this project on time.</t>
+          <t>comes despite intense pressure from Chinese EV makers.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>He promised to be there for her, come hell or high water.</t>
+          <t>The CEO was under intense pressure to deliver positive quarterly results after recent setbacks.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ENG-20260527-454</t>
+          <t>ENG-20260527-554</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4800,44 +4800,44 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>cross that bridge when we come to it</t>
+          <t>hit hardest</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>/krɒs ðæt brɪdʒ wɛn wiː kʌm tuː ɪt/</t>
+          <t>/hɪt ˈhɑːrdɪst/</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>닥쳐서 해결하다, 미리 걱정하지 않다</t>
+          <t>가장 큰 타격을 받다</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>I know there might be a problem with funding, but we'll cross that bridge when we come to it.</t>
+          <t>Mortgage rates rose to the highest level in nine months, hitting refinance demand hardest.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>We don't know yet if we'll need extra staff; we'll cross that bridge when we come to it.</t>
+          <t>Small businesses were hit hardest by the economic downturn and lockdown measures.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ENG-20260527-455</t>
+          <t>ENG-20260527-555</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4847,44 +4847,44 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>cut to the chase</t>
+          <t>face a rise in</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>/kʌt tuː ðə tʃeɪs/</t>
+          <t>/feɪs ə raɪz ɪn/</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>바로 본론으로 들어가다</t>
+          <t>~의 증가에 직면하다</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Let's cut to the chase and discuss the main issue without further delay.</t>
+          <t>Low-income households face ‘remarkable’ rise in food insecurity</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>I don't have much time, so please just cut to the chase.</t>
+          <t>Many countries are expected to face a rise in unemployment due to global economic shifts.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ENG-20260527-456</t>
+          <t>ENG-20260527-556</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4899,39 +4899,39 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>don't put all your eggs in one basket</t>
+          <t>be more active than</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>/doʊnt pʊt ɔːl jʊər ɛɡz ɪn wʌn ˈbɑːskɪt/</t>
+          <t>/bi mɔːr ˈæktɪv ðæn/</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>모든 것을 한 곳에 집중하지 마라, 분산 투자해라</t>
+          <t>~보다 더 활발하다/활동적이다</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>It's wise not to put all your eggs in one basket, especially when investing in volatile stocks.</t>
+          <t>Homebuyers also pulled back but were still more active than last year.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>When looking for a job, don't put all your eggs in one basket; apply to multiple companies.</t>
+          <t>Investors are typically more active than usual during periods of market volatility.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ENG-20260527-457</t>
+          <t>ENG-20260527-557</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4946,39 +4946,39 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>easier said than done</t>
+          <t>fall more than (X percent)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>/ˈiːziər sɛd ðæn dʌn/</t>
+          <t>/fɔːl mɔːr ðæn ɛks ˈpɜːrsɛnt/</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>말이야 쉽지, 실행은 어렵다</t>
+          <t>~퍼센트 이상 하락하다</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Saving money during high inflation is easier said than done for many families.</t>
+          <t>Oil prices fall more than 4%</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Quitting smoking is easier said than done for many people.</t>
+          <t>Stock prices are expected to fall more than 5 percent by the end of the trading day.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ENG-20260527-458</t>
+          <t>ENG-20260527-558</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>every cloud has a silver lining</t>
+          <t>be open to everyone</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5003,163 +5003,22 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>/ˈɛvri klaʊd hæz ə ˈsɪlvər ˈlaɪnɪŋ/</t>
+          <t>/bi ˈoʊpən tuː ˈɛvriˌwʌn/</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>모든 불행에는 한 줄기 희망이 있다, 전화위복</t>
+          <t>모두에게 개방되다; 모두에게 열려 있다</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Losing that job was tough, but I found a better one. Every cloud has a silver lining.</t>
+          <t>Strait of Hormuz...is 'going to be open to everybody.'</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Even during difficult times, remember that every cloud has a silver lining.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>ENG-20260527-459</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Friends</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>get a taste of one's own medicine</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>idiom</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>/ɡɛt ə teɪst ɒv wʌnz oʊn ˈmɛdɪsɪn/</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>자신이 남에게 행했던 나쁜 일을 그대로 당하다, 자업자득</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>After constantly criticizing his colleagues, he finally got a taste of his own medicine when his project failed.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>She was always spreading rumors, and now she's getting a taste of her own medicine.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>ENG-20260527-460</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Friends</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>get out of hand</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>idiom</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>/ɡɛt aʊt ɒv hænd/</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>통제 불능이 되다, 걷잡을 수 없게 되다</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>The party started to get out of hand, so we decided to leave early.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>If we don't address these small issues now, they might get out of hand later.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>ENG-20260527-461</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>HBR</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>get the ball rolling</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>idiom</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>/ɡɛt ðə bɔːl ˈroʊlɪŋ/</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>일을 시작하다, 추진하다</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Let's get the ball rolling on this new marketing campaign right away.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>We need to get the ball rolling on our preparations for the annual conference.</t>
+          <t>The new public library will be open to everyone, regardless of age or background.</t>
         </is>
       </c>
     </row>
